--- a/artfynd/A 32992-2026 artfynd.xlsx
+++ b/artfynd/A 32992-2026 artfynd.xlsx
@@ -1278,7 +1278,7 @@
         <v>714526</v>
       </c>
       <c r="R7" t="n">
-        <v>7335207</v>
+        <v>7335206</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -9494,7 +9494,7 @@
         <v>714526</v>
       </c>
       <c r="R80" t="n">
-        <v>7335207</v>
+        <v>7335206</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>

--- a/artfynd/A 32992-2026 artfynd.xlsx
+++ b/artfynd/A 32992-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136585485</v>
       </c>
       <c r="B2" t="n">
-        <v>92348</v>
+        <v>92351</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136585503</v>
       </c>
       <c r="B3" t="n">
-        <v>92348</v>
+        <v>92351</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136585525</v>
       </c>
       <c r="B4" t="n">
-        <v>92348</v>
+        <v>92351</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136591351</v>
       </c>
       <c r="B5" t="n">
-        <v>92348</v>
+        <v>92351</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>714526</v>
       </c>
       <c r="R7" t="n">
-        <v>7335206</v>
+        <v>7335207</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1360,7 +1360,7 @@
         <v>136585507</v>
       </c>
       <c r="B8" t="n">
-        <v>92281</v>
+        <v>92284</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>136591291</v>
       </c>
       <c r="B9" t="n">
-        <v>92281</v>
+        <v>92284</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>136585492</v>
       </c>
       <c r="B10" t="n">
-        <v>91111</v>
+        <v>91113</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>136585497</v>
       </c>
       <c r="B11" t="n">
-        <v>91111</v>
+        <v>91113</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>136585498</v>
       </c>
       <c r="B12" t="n">
-        <v>91111</v>
+        <v>91113</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>136585514</v>
       </c>
       <c r="B13" t="n">
-        <v>91111</v>
+        <v>91113</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>136585517</v>
       </c>
       <c r="B14" t="n">
-        <v>91111</v>
+        <v>91113</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>136585528</v>
       </c>
       <c r="B15" t="n">
-        <v>91111</v>
+        <v>91113</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>136585530</v>
       </c>
       <c r="B16" t="n">
-        <v>91111</v>
+        <v>91113</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>136585533</v>
       </c>
       <c r="B17" t="n">
-        <v>91111</v>
+        <v>91113</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>136591293</v>
       </c>
       <c r="B18" t="n">
-        <v>91111</v>
+        <v>91113</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>136591296</v>
       </c>
       <c r="B19" t="n">
-        <v>91111</v>
+        <v>91113</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>136591302</v>
       </c>
       <c r="B20" t="n">
-        <v>91111</v>
+        <v>91113</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>136591331</v>
       </c>
       <c r="B21" t="n">
-        <v>91111</v>
+        <v>91113</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>136591333</v>
       </c>
       <c r="B22" t="n">
-        <v>91111</v>
+        <v>91113</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>136591298</v>
       </c>
       <c r="B23" t="n">
-        <v>93416</v>
+        <v>93419</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>136591346</v>
       </c>
       <c r="B24" t="n">
-        <v>93416</v>
+        <v>93419</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>136585490</v>
       </c>
       <c r="B25" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>136585499</v>
       </c>
       <c r="B26" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>136585516</v>
       </c>
       <c r="B27" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>136585521</v>
       </c>
       <c r="B28" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         <v>136591340</v>
       </c>
       <c r="B29" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
         <v>136585500</v>
       </c>
       <c r="B30" t="n">
-        <v>92024</v>
+        <v>92027</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         <v>136585506</v>
       </c>
       <c r="B31" t="n">
-        <v>92024</v>
+        <v>92027</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         <v>136585488</v>
       </c>
       <c r="B33" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>136585491</v>
       </c>
       <c r="B34" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
         <v>136585495</v>
       </c>
       <c r="B35" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4518,7 +4518,7 @@
         <v>136585509</v>
       </c>
       <c r="B36" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4630,7 +4630,7 @@
         <v>136585518</v>
       </c>
       <c r="B37" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4742,7 +4742,7 @@
         <v>136585522</v>
       </c>
       <c r="B38" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>136585527</v>
       </c>
       <c r="B39" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>136591316</v>
       </c>
       <c r="B40" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>136591335</v>
       </c>
       <c r="B41" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>136591338</v>
       </c>
       <c r="B42" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
         <v>136591345</v>
       </c>
       <c r="B43" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         <v>136591354</v>
       </c>
       <c r="B44" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5654,7 +5654,7 @@
         <v>136585489</v>
       </c>
       <c r="B46" t="n">
-        <v>93404</v>
+        <v>93407</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5766,7 +5766,7 @@
         <v>136591295</v>
       </c>
       <c r="B47" t="n">
-        <v>93404</v>
+        <v>93407</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5878,7 +5878,7 @@
         <v>136591314</v>
       </c>
       <c r="B48" t="n">
-        <v>93404</v>
+        <v>93407</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5990,7 +5990,7 @@
         <v>136591339</v>
       </c>
       <c r="B49" t="n">
-        <v>93404</v>
+        <v>93407</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
         <v>136591297</v>
       </c>
       <c r="B52" t="n">
-        <v>93044</v>
+        <v>93047</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
         <v>136591303</v>
       </c>
       <c r="B53" t="n">
-        <v>93044</v>
+        <v>93047</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6548,7 +6548,7 @@
         <v>136591307</v>
       </c>
       <c r="B54" t="n">
-        <v>93044</v>
+        <v>93047</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6660,7 +6660,7 @@
         <v>136585526</v>
       </c>
       <c r="B55" t="n">
-        <v>93426</v>
+        <v>93429</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -9494,7 +9494,7 @@
         <v>714526</v>
       </c>
       <c r="R80" t="n">
-        <v>7335206</v>
+        <v>7335207</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -11937,7 +11937,7 @@
         <v>136591313</v>
       </c>
       <c r="B102" t="n">
-        <v>93431</v>
+        <v>93434</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12061,7 +12061,7 @@
         <v>136591334</v>
       </c>
       <c r="B103" t="n">
-        <v>93431</v>
+        <v>93434</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>

--- a/artfynd/A 32992-2026 artfynd.xlsx
+++ b/artfynd/A 32992-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136585485</v>
       </c>
       <c r="B2" t="n">
-        <v>92351</v>
+        <v>92352</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136585503</v>
       </c>
       <c r="B3" t="n">
-        <v>92351</v>
+        <v>92352</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136585525</v>
       </c>
       <c r="B4" t="n">
-        <v>92351</v>
+        <v>92352</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136591351</v>
       </c>
       <c r="B5" t="n">
-        <v>92351</v>
+        <v>92352</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>714526</v>
       </c>
       <c r="R7" t="n">
-        <v>7335207</v>
+        <v>7335206</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1360,7 +1360,7 @@
         <v>136585507</v>
       </c>
       <c r="B8" t="n">
-        <v>92284</v>
+        <v>92285</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>136591291</v>
       </c>
       <c r="B9" t="n">
-        <v>92284</v>
+        <v>92285</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>136591298</v>
       </c>
       <c r="B23" t="n">
-        <v>93419</v>
+        <v>93420</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>136591346</v>
       </c>
       <c r="B24" t="n">
-        <v>93419</v>
+        <v>93420</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>136585490</v>
       </c>
       <c r="B25" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>136585499</v>
       </c>
       <c r="B26" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>136585516</v>
       </c>
       <c r="B27" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>136585521</v>
       </c>
       <c r="B28" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         <v>136591340</v>
       </c>
       <c r="B29" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
         <v>136585500</v>
       </c>
       <c r="B30" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         <v>136585506</v>
       </c>
       <c r="B31" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         <v>136585488</v>
       </c>
       <c r="B33" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>136585491</v>
       </c>
       <c r="B34" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
         <v>136585495</v>
       </c>
       <c r="B35" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4518,7 +4518,7 @@
         <v>136585509</v>
       </c>
       <c r="B36" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4630,7 +4630,7 @@
         <v>136585518</v>
       </c>
       <c r="B37" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4742,7 +4742,7 @@
         <v>136585522</v>
       </c>
       <c r="B38" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>136585527</v>
       </c>
       <c r="B39" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>136591316</v>
       </c>
       <c r="B40" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>136591335</v>
       </c>
       <c r="B41" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>136591338</v>
       </c>
       <c r="B42" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
         <v>136591345</v>
       </c>
       <c r="B43" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         <v>136591354</v>
       </c>
       <c r="B44" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5654,7 +5654,7 @@
         <v>136585489</v>
       </c>
       <c r="B46" t="n">
-        <v>93407</v>
+        <v>93408</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5766,7 +5766,7 @@
         <v>136591295</v>
       </c>
       <c r="B47" t="n">
-        <v>93407</v>
+        <v>93408</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5878,7 +5878,7 @@
         <v>136591314</v>
       </c>
       <c r="B48" t="n">
-        <v>93407</v>
+        <v>93408</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5990,7 +5990,7 @@
         <v>136591339</v>
       </c>
       <c r="B49" t="n">
-        <v>93407</v>
+        <v>93408</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
         <v>136591297</v>
       </c>
       <c r="B52" t="n">
-        <v>93047</v>
+        <v>93048</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
         <v>136591303</v>
       </c>
       <c r="B53" t="n">
-        <v>93047</v>
+        <v>93048</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6548,7 +6548,7 @@
         <v>136591307</v>
       </c>
       <c r="B54" t="n">
-        <v>93047</v>
+        <v>93048</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6660,7 +6660,7 @@
         <v>136585526</v>
       </c>
       <c r="B55" t="n">
-        <v>93429</v>
+        <v>93430</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -9494,7 +9494,7 @@
         <v>714526</v>
       </c>
       <c r="R80" t="n">
-        <v>7335207</v>
+        <v>7335206</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -11937,7 +11937,7 @@
         <v>136591313</v>
       </c>
       <c r="B102" t="n">
-        <v>93434</v>
+        <v>93435</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12061,7 +12061,7 @@
         <v>136591334</v>
       </c>
       <c r="B103" t="n">
-        <v>93434</v>
+        <v>93435</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>

--- a/artfynd/A 32992-2026 artfynd.xlsx
+++ b/artfynd/A 32992-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136585485</v>
       </c>
       <c r="B2" t="n">
-        <v>92352</v>
+        <v>92357</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136585503</v>
       </c>
       <c r="B3" t="n">
-        <v>92352</v>
+        <v>92357</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136585525</v>
       </c>
       <c r="B4" t="n">
-        <v>92352</v>
+        <v>92357</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136591351</v>
       </c>
       <c r="B5" t="n">
-        <v>92352</v>
+        <v>92357</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136585531</v>
       </c>
       <c r="B6" t="n">
-        <v>79140</v>
+        <v>79142</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136591319</v>
       </c>
       <c r="B7" t="n">
-        <v>79140</v>
+        <v>79142</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>136585507</v>
       </c>
       <c r="B8" t="n">
-        <v>92285</v>
+        <v>92290</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>136591291</v>
       </c>
       <c r="B9" t="n">
-        <v>92285</v>
+        <v>92290</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>136585492</v>
       </c>
       <c r="B10" t="n">
-        <v>91113</v>
+        <v>91115</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>136585497</v>
       </c>
       <c r="B11" t="n">
-        <v>91113</v>
+        <v>91115</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>136585498</v>
       </c>
       <c r="B12" t="n">
-        <v>91113</v>
+        <v>91115</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>136585514</v>
       </c>
       <c r="B13" t="n">
-        <v>91113</v>
+        <v>91115</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>136585517</v>
       </c>
       <c r="B14" t="n">
-        <v>91113</v>
+        <v>91115</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>136585528</v>
       </c>
       <c r="B15" t="n">
-        <v>91113</v>
+        <v>91115</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>136585530</v>
       </c>
       <c r="B16" t="n">
-        <v>91113</v>
+        <v>91115</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>136585533</v>
       </c>
       <c r="B17" t="n">
-        <v>91113</v>
+        <v>91115</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>136591293</v>
       </c>
       <c r="B18" t="n">
-        <v>91113</v>
+        <v>91115</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>136591296</v>
       </c>
       <c r="B19" t="n">
-        <v>91113</v>
+        <v>91115</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>136591302</v>
       </c>
       <c r="B20" t="n">
-        <v>91113</v>
+        <v>91115</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>136591331</v>
       </c>
       <c r="B21" t="n">
-        <v>91113</v>
+        <v>91115</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>136591333</v>
       </c>
       <c r="B22" t="n">
-        <v>91113</v>
+        <v>91115</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>136591298</v>
       </c>
       <c r="B23" t="n">
-        <v>93420</v>
+        <v>93425</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>136591346</v>
       </c>
       <c r="B24" t="n">
-        <v>93420</v>
+        <v>93425</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>136585490</v>
       </c>
       <c r="B25" t="n">
-        <v>92159</v>
+        <v>92164</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>136585499</v>
       </c>
       <c r="B26" t="n">
-        <v>92159</v>
+        <v>92164</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>136585516</v>
       </c>
       <c r="B27" t="n">
-        <v>92159</v>
+        <v>92164</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>136585521</v>
       </c>
       <c r="B28" t="n">
-        <v>92159</v>
+        <v>92164</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         <v>136591340</v>
       </c>
       <c r="B29" t="n">
-        <v>92159</v>
+        <v>92164</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
         <v>136585500</v>
       </c>
       <c r="B30" t="n">
-        <v>92028</v>
+        <v>92033</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         <v>136585506</v>
       </c>
       <c r="B31" t="n">
-        <v>92028</v>
+        <v>92033</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         <v>136585488</v>
       </c>
       <c r="B33" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>136585491</v>
       </c>
       <c r="B34" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
         <v>136585495</v>
       </c>
       <c r="B35" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4518,7 +4518,7 @@
         <v>136585509</v>
       </c>
       <c r="B36" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4630,7 +4630,7 @@
         <v>136585518</v>
       </c>
       <c r="B37" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4742,7 +4742,7 @@
         <v>136585522</v>
       </c>
       <c r="B38" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>136585527</v>
       </c>
       <c r="B39" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>136591316</v>
       </c>
       <c r="B40" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>136591335</v>
       </c>
       <c r="B41" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>136591338</v>
       </c>
       <c r="B42" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
         <v>136591345</v>
       </c>
       <c r="B43" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         <v>136591354</v>
       </c>
       <c r="B44" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5654,7 +5654,7 @@
         <v>136585489</v>
       </c>
       <c r="B46" t="n">
-        <v>93408</v>
+        <v>93413</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5766,7 +5766,7 @@
         <v>136591295</v>
       </c>
       <c r="B47" t="n">
-        <v>93408</v>
+        <v>93413</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5878,7 +5878,7 @@
         <v>136591314</v>
       </c>
       <c r="B48" t="n">
-        <v>93408</v>
+        <v>93413</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5990,7 +5990,7 @@
         <v>136591339</v>
       </c>
       <c r="B49" t="n">
-        <v>93408</v>
+        <v>93413</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
         <v>136591297</v>
       </c>
       <c r="B52" t="n">
-        <v>93048</v>
+        <v>93053</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
         <v>136591303</v>
       </c>
       <c r="B53" t="n">
-        <v>93048</v>
+        <v>93053</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6548,7 +6548,7 @@
         <v>136591307</v>
       </c>
       <c r="B54" t="n">
-        <v>93048</v>
+        <v>93053</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6660,7 +6660,7 @@
         <v>136585526</v>
       </c>
       <c r="B55" t="n">
-        <v>93430</v>
+        <v>93435</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6772,7 +6772,7 @@
         <v>136585493</v>
       </c>
       <c r="B56" t="n">
-        <v>78877</v>
+        <v>78879</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6884,7 +6884,7 @@
         <v>136585494</v>
       </c>
       <c r="B57" t="n">
-        <v>78877</v>
+        <v>78879</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
         <v>136585520</v>
       </c>
       <c r="B58" t="n">
-        <v>78877</v>
+        <v>78879</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         <v>136591289</v>
       </c>
       <c r="B59" t="n">
-        <v>78877</v>
+        <v>78879</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7220,7 +7220,7 @@
         <v>136591292</v>
       </c>
       <c r="B60" t="n">
-        <v>78877</v>
+        <v>78879</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7332,7 +7332,7 @@
         <v>136591299</v>
       </c>
       <c r="B61" t="n">
-        <v>78877</v>
+        <v>78879</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>136591305</v>
       </c>
       <c r="B62" t="n">
-        <v>78877</v>
+        <v>78879</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         <v>136591308</v>
       </c>
       <c r="B63" t="n">
-        <v>78877</v>
+        <v>78879</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7668,7 +7668,7 @@
         <v>136591312</v>
       </c>
       <c r="B64" t="n">
-        <v>78877</v>
+        <v>78879</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         <v>136591318</v>
       </c>
       <c r="B65" t="n">
-        <v>78877</v>
+        <v>78879</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7892,7 +7892,7 @@
         <v>136591322</v>
       </c>
       <c r="B66" t="n">
-        <v>78877</v>
+        <v>78879</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8004,7 +8004,7 @@
         <v>136591325</v>
       </c>
       <c r="B67" t="n">
-        <v>78877</v>
+        <v>78879</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8116,7 +8116,7 @@
         <v>136591332</v>
       </c>
       <c r="B68" t="n">
-        <v>78877</v>
+        <v>78879</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8228,7 +8228,7 @@
         <v>136591337</v>
       </c>
       <c r="B69" t="n">
-        <v>78877</v>
+        <v>78879</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8340,7 +8340,7 @@
         <v>136591342</v>
       </c>
       <c r="B70" t="n">
-        <v>78877</v>
+        <v>78879</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8452,7 +8452,7 @@
         <v>136591348</v>
       </c>
       <c r="B71" t="n">
-        <v>78877</v>
+        <v>78879</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8564,7 +8564,7 @@
         <v>136591352</v>
       </c>
       <c r="B72" t="n">
-        <v>78877</v>
+        <v>78879</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8898,7 +8898,7 @@
         <v>136585487</v>
       </c>
       <c r="B75" t="n">
-        <v>79231</v>
+        <v>79233</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
         <v>136585524</v>
       </c>
       <c r="B76" t="n">
-        <v>79231</v>
+        <v>79233</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9123,7 +9123,7 @@
         <v>136591288</v>
       </c>
       <c r="B77" t="n">
-        <v>79231</v>
+        <v>79233</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9235,7 +9235,7 @@
         <v>136591300</v>
       </c>
       <c r="B78" t="n">
-        <v>79231</v>
+        <v>79233</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9347,7 +9347,7 @@
         <v>136585513</v>
       </c>
       <c r="B79" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9459,7 +9459,7 @@
         <v>136585515</v>
       </c>
       <c r="B80" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9571,7 +9571,7 @@
         <v>136591344</v>
       </c>
       <c r="B81" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9683,7 +9683,7 @@
         <v>136591309</v>
       </c>
       <c r="B82" t="n">
-        <v>78478</v>
+        <v>78480</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9795,7 +9795,7 @@
         <v>136591323</v>
       </c>
       <c r="B83" t="n">
-        <v>78478</v>
+        <v>78480</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9907,7 +9907,7 @@
         <v>136591343</v>
       </c>
       <c r="B84" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10027,7 +10027,7 @@
         <v>136591304</v>
       </c>
       <c r="B85" t="n">
-        <v>58110</v>
+        <v>58112</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
         <v>136585501</v>
       </c>
       <c r="B86" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10259,7 +10259,7 @@
         <v>136585512</v>
       </c>
       <c r="B87" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10371,7 +10371,7 @@
         <v>136585523</v>
       </c>
       <c r="B88" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10483,7 +10483,7 @@
         <v>136585529</v>
       </c>
       <c r="B89" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10595,7 +10595,7 @@
         <v>136585532</v>
       </c>
       <c r="B90" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10707,7 +10707,7 @@
         <v>136591287</v>
       </c>
       <c r="B91" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10819,7 +10819,7 @@
         <v>136591306</v>
       </c>
       <c r="B92" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10931,7 +10931,7 @@
         <v>136591311</v>
       </c>
       <c r="B93" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11043,7 +11043,7 @@
         <v>136591317</v>
       </c>
       <c r="B94" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11155,7 +11155,7 @@
         <v>136591324</v>
       </c>
       <c r="B95" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11267,7 +11267,7 @@
         <v>136591350</v>
       </c>
       <c r="B96" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11379,7 +11379,7 @@
         <v>136591353</v>
       </c>
       <c r="B97" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11491,7 +11491,7 @@
         <v>136591355</v>
       </c>
       <c r="B98" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11714,7 +11714,7 @@
         <v>136591301</v>
       </c>
       <c r="B100" t="n">
-        <v>80064</v>
+        <v>80066</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11937,7 +11937,7 @@
         <v>136591313</v>
       </c>
       <c r="B102" t="n">
-        <v>93435</v>
+        <v>93440</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12061,7 +12061,7 @@
         <v>136591334</v>
       </c>
       <c r="B103" t="n">
-        <v>93435</v>
+        <v>93440</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12182,7 +12182,7 @@
         <v>136591294</v>
       </c>
       <c r="B104" t="n">
-        <v>79497</v>
+        <v>79499</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12294,7 +12294,7 @@
         <v>136591321</v>
       </c>
       <c r="B105" t="n">
-        <v>79497</v>
+        <v>79499</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12419,7 +12419,7 @@
         <v>136591341</v>
       </c>
       <c r="B106" t="n">
-        <v>79497</v>
+        <v>79499</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>

--- a/artfynd/A 32992-2026 artfynd.xlsx
+++ b/artfynd/A 32992-2026 artfynd.xlsx
@@ -1278,7 +1278,7 @@
         <v>714526</v>
       </c>
       <c r="R7" t="n">
-        <v>7335206</v>
+        <v>7335207</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -9494,7 +9494,7 @@
         <v>714526</v>
       </c>
       <c r="R80" t="n">
-        <v>7335206</v>
+        <v>7335207</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>

--- a/artfynd/A 32992-2026 artfynd.xlsx
+++ b/artfynd/A 32992-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ106"/>
+  <dimension ref="A1:AZ114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>136585485</v>
       </c>
       <c r="B2" t="n">
-        <v>92357</v>
+        <v>92359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136585503</v>
       </c>
       <c r="B3" t="n">
-        <v>92357</v>
+        <v>92359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136585525</v>
       </c>
       <c r="B4" t="n">
-        <v>92357</v>
+        <v>92359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136591351</v>
       </c>
       <c r="B5" t="n">
-        <v>92357</v>
+        <v>92359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>714526</v>
       </c>
       <c r="R7" t="n">
-        <v>7335207</v>
+        <v>7335206</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1357,45 +1357,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136585507</v>
+        <v>136858049</v>
       </c>
       <c r="B8" t="n">
-        <v>92290</v>
+        <v>79142</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Liejbebákte, Lu lm</t>
+          <t>Tellejåkk, Lu lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>714601</v>
+        <v>714516</v>
       </c>
       <c r="R8" t="n">
-        <v>7335098</v>
+        <v>7335060</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1422,22 +1426,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1452,62 +1461,66 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136585507</t>
+          <t>https://artportalen.se/Sighting/136858049</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>136591291</v>
+        <v>136858050</v>
       </c>
       <c r="B9" t="n">
-        <v>92290</v>
+        <v>79142</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Liejbebákte, Tellejokk, S Jokkmokk, Lu lm</t>
+          <t>Tellejåkk, Lu lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>714689</v>
+        <v>714502</v>
       </c>
       <c r="R9" t="n">
-        <v>7334937</v>
+        <v>7335093</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1534,22 +1547,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1558,72 +1576,75 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136591291</t>
+          <t>https://artportalen.se/Sighting/136858050</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>136585492</v>
+        <v>136857943</v>
       </c>
       <c r="B10" t="n">
-        <v>91115</v>
+        <v>89375</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1962</v>
+        <v>816</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Smultronkantarell</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Aphroditeola olida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Quél.) Redhead &amp; Manfr.Binder</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Liejbebákte, Lu lm</t>
+          <t>Tellejåkk, Lu lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>714657</v>
+        <v>714498</v>
       </c>
       <c r="R10" t="n">
-        <v>7335002</v>
+        <v>7335061</v>
       </c>
       <c r="S10" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1647,22 +1668,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1677,49 +1703,49 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136585492</t>
+          <t>https://artportalen.se/Sighting/136857943</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>136585497</v>
+        <v>136585507</v>
       </c>
       <c r="B11" t="n">
-        <v>91115</v>
+        <v>92292</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1962</v>
+        <v>1503</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1729,10 +1755,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>714616</v>
+        <v>714601</v>
       </c>
       <c r="R11" t="n">
-        <v>7335046</v>
+        <v>7335098</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1764,7 +1790,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1774,7 +1800,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1800,54 +1826,54 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136585497</t>
+          <t>https://artportalen.se/Sighting/136585507</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>136585498</v>
+        <v>136591291</v>
       </c>
       <c r="B12" t="n">
-        <v>91115</v>
+        <v>92292</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1962</v>
+        <v>1503</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Liejbebákte, Lu lm</t>
+          <t>Liejbebákte, Tellejokk, S Jokkmokk, Lu lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>714623</v>
+        <v>714689</v>
       </c>
       <c r="R12" t="n">
-        <v>7335056</v>
+        <v>7334937</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1876,7 +1902,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1886,7 +1912,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1895,33 +1921,34 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136585498</t>
+          <t>https://artportalen.se/Sighting/136591291</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>136585514</v>
+        <v>136585492</v>
       </c>
       <c r="B13" t="n">
-        <v>91115</v>
+        <v>91117</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1953,13 +1980,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>714555</v>
+        <v>714657</v>
       </c>
       <c r="R13" t="n">
-        <v>7335162</v>
+        <v>7335002</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1988,7 +2015,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1998,7 +2025,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2024,16 +2051,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136585514</t>
+          <t>https://artportalen.se/Sighting/136585492</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>136585517</v>
+        <v>136585497</v>
       </c>
       <c r="B14" t="n">
-        <v>91115</v>
+        <v>91117</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2065,13 +2092,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>714643</v>
+        <v>714616</v>
       </c>
       <c r="R14" t="n">
-        <v>7335242</v>
+        <v>7335046</v>
       </c>
       <c r="S14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2100,7 +2127,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2110,7 +2137,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2136,16 +2163,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136585517</t>
+          <t>https://artportalen.se/Sighting/136585497</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>136585528</v>
+        <v>136585498</v>
       </c>
       <c r="B15" t="n">
-        <v>91115</v>
+        <v>91117</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2177,13 +2204,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>714585</v>
+        <v>714623</v>
       </c>
       <c r="R15" t="n">
-        <v>7334950</v>
+        <v>7335056</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2212,7 +2239,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2222,7 +2249,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2248,16 +2275,16 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136585528</t>
+          <t>https://artportalen.se/Sighting/136585498</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>136585530</v>
+        <v>136585514</v>
       </c>
       <c r="B16" t="n">
-        <v>91115</v>
+        <v>91117</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2289,10 +2316,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>714579</v>
+        <v>714555</v>
       </c>
       <c r="R16" t="n">
-        <v>7334850</v>
+        <v>7335162</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2324,7 +2351,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2334,7 +2361,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2360,16 +2387,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136585530</t>
+          <t>https://artportalen.se/Sighting/136585514</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>136585533</v>
+        <v>136585517</v>
       </c>
       <c r="B17" t="n">
-        <v>91115</v>
+        <v>91117</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2401,13 +2428,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>714661</v>
+        <v>714643</v>
       </c>
       <c r="R17" t="n">
-        <v>7334843</v>
+        <v>7335242</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2436,7 +2463,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2446,7 +2473,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2472,16 +2499,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136585533</t>
+          <t>https://artportalen.se/Sighting/136585517</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>136591293</v>
+        <v>136585528</v>
       </c>
       <c r="B18" t="n">
-        <v>91115</v>
+        <v>91117</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2509,17 +2536,17 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Liejbebákte, Tellejokk, S Jokkmokk, Lu lm</t>
+          <t>Liejbebákte, Lu lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>714692</v>
+        <v>714585</v>
       </c>
       <c r="R18" t="n">
-        <v>7334961</v>
+        <v>7334950</v>
       </c>
       <c r="S18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2548,7 +2575,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2558,7 +2585,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2573,27 +2600,27 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136591293</t>
+          <t>https://artportalen.se/Sighting/136585528</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>136591296</v>
+        <v>136585530</v>
       </c>
       <c r="B19" t="n">
-        <v>91115</v>
+        <v>91117</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2619,22 +2646,19 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Liejbebákte, Tellejokk, S Jokkmokk, Lu lm</t>
+          <t>Liejbebákte, Lu lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>714686</v>
+        <v>714579</v>
       </c>
       <c r="R19" t="n">
-        <v>7334984</v>
+        <v>7334850</v>
       </c>
       <c r="S19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2663,7 +2687,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2673,43 +2697,42 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF19" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136591296</t>
+          <t>https://artportalen.se/Sighting/136585530</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>136591302</v>
+        <v>136585533</v>
       </c>
       <c r="B20" t="n">
-        <v>91115</v>
+        <v>91117</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2737,14 +2760,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Liejbebákte, Tellejokk, S Jokkmokk, Lu lm</t>
+          <t>Liejbebákte, Lu lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>714624</v>
+        <v>714661</v>
       </c>
       <c r="R20" t="n">
-        <v>7335052</v>
+        <v>7334843</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2776,7 +2799,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2786,7 +2809,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2801,27 +2824,27 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136591302</t>
+          <t>https://artportalen.se/Sighting/136585533</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>136591331</v>
+        <v>136591293</v>
       </c>
       <c r="B21" t="n">
-        <v>91115</v>
+        <v>91117</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2853,13 +2876,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>714620</v>
+        <v>714692</v>
       </c>
       <c r="R21" t="n">
-        <v>7335269</v>
+        <v>7334961</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2888,7 +2911,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2898,7 +2921,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2924,16 +2947,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136591331</t>
+          <t>https://artportalen.se/Sighting/136591293</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>136591333</v>
+        <v>136591296</v>
       </c>
       <c r="B22" t="n">
-        <v>91115</v>
+        <v>91117</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2959,19 +2982,22 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Liejbebákte, Tellejokk, S Jokkmokk, Lu lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>714641</v>
+        <v>714686</v>
       </c>
       <c r="R22" t="n">
-        <v>7335275</v>
+        <v>7334984</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3000,7 +3026,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3010,15 +3036,16 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3036,62 +3063,51 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136591333</t>
+          <t>https://artportalen.se/Sighting/136591296</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>136591298</v>
+        <v>136591302</v>
       </c>
       <c r="B23" t="n">
-        <v>93425</v>
+        <v>91117</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2059</v>
+        <v>1962</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Liejbebákte, Tellejokk, S Jokkmokk, Lu lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>714660</v>
+        <v>714624</v>
       </c>
       <c r="R23" t="n">
-        <v>7335006</v>
+        <v>7335052</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3123,7 +3139,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3133,12 +3149,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:08</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Blågrå fotbas. Smakar väldigt "skrovligt", strävt, bittert.</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3147,7 +3158,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3165,38 +3175,38 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136591298</t>
+          <t>https://artportalen.se/Sighting/136591302</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>136591346</v>
+        <v>136591331</v>
       </c>
       <c r="B24" t="n">
-        <v>93425</v>
+        <v>91117</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2059</v>
+        <v>1962</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3206,10 +3216,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>714702</v>
+        <v>714620</v>
       </c>
       <c r="R24" t="n">
-        <v>7335004</v>
+        <v>7335269</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3241,7 +3251,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3251,7 +3261,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3277,16 +3287,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136591346</t>
+          <t>https://artportalen.se/Sighting/136591331</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>136585490</v>
+        <v>136591333</v>
       </c>
       <c r="B25" t="n">
-        <v>92164</v>
+        <v>91117</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3294,37 +3304,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2079</v>
+        <v>1962</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Liejbebákte, Lu lm</t>
+          <t>Liejbebákte, Tellejokk, S Jokkmokk, Lu lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>714687</v>
+        <v>714641</v>
       </c>
       <c r="R25" t="n">
-        <v>7334973</v>
+        <v>7335275</v>
       </c>
       <c r="S25" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3353,7 +3363,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3363,7 +3373,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3372,34 +3382,33 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136585490</t>
+          <t>https://artportalen.se/Sighting/136591333</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>136585499</v>
+        <v>136857931</v>
       </c>
       <c r="B26" t="n">
-        <v>92164</v>
+        <v>91117</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3407,37 +3416,41 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2079</v>
+        <v>1962</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Liejbebákte, Lu lm</t>
+          <t>Tellejåkk, Lu lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>714622</v>
+        <v>714510</v>
       </c>
       <c r="R26" t="n">
-        <v>7335059</v>
+        <v>7335011</v>
       </c>
       <c r="S26" t="n">
-        <v>66</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3461,22 +3474,27 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3491,65 +3509,76 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136585499</t>
+          <t>https://artportalen.se/Sighting/136857931</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>136585516</v>
+        <v>136591298</v>
       </c>
       <c r="B27" t="n">
-        <v>92164</v>
+        <v>93427</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2079</v>
+        <v>2059</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Liejbebákte, Lu lm</t>
+          <t>Liejbebákte, Tellejokk, S Jokkmokk, Lu lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>714605</v>
+        <v>714660</v>
       </c>
       <c r="R27" t="n">
-        <v>7335259</v>
+        <v>7335006</v>
       </c>
       <c r="S27" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3578,7 +3607,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3588,7 +3617,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Blågrå fotbas. Smakar väldigt "skrovligt", strävt, bittert.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3597,68 +3631,69 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136585516</t>
+          <t>https://artportalen.se/Sighting/136591298</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>136585521</v>
+        <v>136591346</v>
       </c>
       <c r="B28" t="n">
-        <v>92164</v>
+        <v>93427</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2079</v>
+        <v>2059</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Liejbebákte, Lu lm</t>
+          <t>Liejbebákte, Tellejokk, S Jokkmokk, Lu lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>714661</v>
+        <v>714702</v>
       </c>
       <c r="R28" t="n">
-        <v>7335205</v>
+        <v>7335004</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3690,7 +3725,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3700,7 +3735,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3715,27 +3750,27 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136585521</t>
+          <t>https://artportalen.se/Sighting/136591346</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>136591340</v>
+        <v>136585490</v>
       </c>
       <c r="B29" t="n">
-        <v>92164</v>
+        <v>92166</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3763,17 +3798,17 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Liejbebákte, Tellejokk, S Jokkmokk, Lu lm</t>
+          <t>Liejbebákte, Lu lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>714640</v>
+        <v>714687</v>
       </c>
       <c r="R29" t="n">
-        <v>7335223</v>
+        <v>7334973</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3802,7 +3837,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3812,7 +3847,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3821,33 +3856,34 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136591340</t>
+          <t>https://artportalen.se/Sighting/136585490</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>136585500</v>
+        <v>136585499</v>
       </c>
       <c r="B30" t="n">
-        <v>92033</v>
+        <v>92166</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3855,21 +3891,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3242</v>
+        <v>2079</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3879,13 +3915,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>714634</v>
+        <v>714622</v>
       </c>
       <c r="R30" t="n">
-        <v>7335060</v>
+        <v>7335059</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>66</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3914,7 +3950,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3924,7 +3960,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3950,16 +3986,16 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136585500</t>
+          <t>https://artportalen.se/Sighting/136585499</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>136585506</v>
+        <v>136585516</v>
       </c>
       <c r="B31" t="n">
-        <v>92033</v>
+        <v>92166</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3967,21 +4003,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3242</v>
+        <v>2079</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3991,13 +4027,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>714618</v>
+        <v>714605</v>
       </c>
       <c r="R31" t="n">
-        <v>7335077</v>
+        <v>7335259</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4026,7 +4062,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4036,7 +4072,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4062,16 +4098,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136585506</t>
+          <t>https://artportalen.se/Sighting/136585516</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129000555</v>
+        <v>136585521</v>
       </c>
       <c r="B32" t="n">
-        <v>93197</v>
+        <v>92166</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4079,41 +4115,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Tellejåkk, Lu lm</t>
+          <t>Liejbebákte, Lu lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>714704</v>
+        <v>714661</v>
       </c>
       <c r="R32" t="n">
-        <v>7335273</v>
+        <v>7335205</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4137,17 +4169,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4162,27 +4199,27 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000555</t>
+          <t>https://artportalen.se/Sighting/136585521</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>136585488</v>
+        <v>136591340</v>
       </c>
       <c r="B33" t="n">
-        <v>93409</v>
+        <v>92166</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4190,37 +4227,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Liejbebákte, Lu lm</t>
+          <t>Liejbebákte, Tellejokk, S Jokkmokk, Lu lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>714692</v>
+        <v>714640</v>
       </c>
       <c r="R33" t="n">
-        <v>7334952</v>
+        <v>7335223</v>
       </c>
       <c r="S33" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4249,7 +4286,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4259,7 +4296,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4274,27 +4311,27 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136585488</t>
+          <t>https://artportalen.se/Sighting/136591340</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>136585491</v>
+        <v>136585500</v>
       </c>
       <c r="B34" t="n">
-        <v>93409</v>
+        <v>92035</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4302,21 +4339,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>3242</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4326,13 +4363,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>714653</v>
+        <v>714634</v>
       </c>
       <c r="R34" t="n">
-        <v>7335007</v>
+        <v>7335060</v>
       </c>
       <c r="S34" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4361,7 +4398,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4371,7 +4408,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4397,16 +4434,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136585491</t>
+          <t>https://artportalen.se/Sighting/136585500</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>136585495</v>
+        <v>136585506</v>
       </c>
       <c r="B35" t="n">
-        <v>93409</v>
+        <v>92035</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4414,21 +4451,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>3242</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4438,10 +4475,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>714625</v>
+        <v>714618</v>
       </c>
       <c r="R35" t="n">
-        <v>7335024</v>
+        <v>7335077</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4473,7 +4510,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4483,7 +4520,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4509,16 +4546,16 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136585495</t>
+          <t>https://artportalen.se/Sighting/136585506</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>136585509</v>
+        <v>129000555</v>
       </c>
       <c r="B36" t="n">
-        <v>93409</v>
+        <v>93197</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4543,20 +4580,24 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Liejbebákte, Lu lm</t>
+          <t>Tellejåkk, Lu lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>714600</v>
+        <v>714704</v>
       </c>
       <c r="R36" t="n">
-        <v>7335115</v>
+        <v>7335273</v>
       </c>
       <c r="S36" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4580,22 +4621,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>13:35</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>13:35</t>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4610,27 +4646,27 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136585509</t>
+          <t>https://artportalen.se/Sighting/129000555</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>136585518</v>
+        <v>136585488</v>
       </c>
       <c r="B37" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4662,13 +4698,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>714643</v>
+        <v>714692</v>
       </c>
       <c r="R37" t="n">
-        <v>7335244</v>
+        <v>7334952</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4697,7 +4733,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4707,7 +4743,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4733,16 +4769,16 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136585518</t>
+          <t>https://artportalen.se/Sighting/136585488</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>136585522</v>
+        <v>136585491</v>
       </c>
       <c r="B38" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4774,13 +4810,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>714681</v>
+        <v>714653</v>
       </c>
       <c r="R38" t="n">
-        <v>7335197</v>
+        <v>7335007</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4809,7 +4845,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4819,7 +4855,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4845,16 +4881,16 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136585522</t>
+          <t>https://artportalen.se/Sighting/136585491</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>136585527</v>
+        <v>136585495</v>
       </c>
       <c r="B39" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4886,13 +4922,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>714655</v>
+        <v>714625</v>
       </c>
       <c r="R39" t="n">
-        <v>7334958</v>
+        <v>7335024</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4921,7 +4957,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4931,7 +4967,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4957,16 +4993,16 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136585527</t>
+          <t>https://artportalen.se/Sighting/136585495</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>136591316</v>
+        <v>136585509</v>
       </c>
       <c r="B40" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4994,17 +5030,17 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Liejbebákte, Tellejokk, S Jokkmokk, Lu lm</t>
+          <t>Liejbebákte, Lu lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>714539</v>
+        <v>714600</v>
       </c>
       <c r="R40" t="n">
-        <v>7335184</v>
+        <v>7335115</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5033,7 +5069,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5043,7 +5079,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5058,27 +5094,27 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136591316</t>
+          <t>https://artportalen.se/Sighting/136585509</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>136591335</v>
+        <v>136585518</v>
       </c>
       <c r="B41" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5106,14 +5142,14 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Liejbebákte, Tellejokk, S Jokkmokk, Lu lm</t>
+          <t>Liejbebákte, Lu lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>714653</v>
+        <v>714643</v>
       </c>
       <c r="R41" t="n">
-        <v>7335255</v>
+        <v>7335244</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5145,7 +5181,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5155,7 +5191,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5170,27 +5206,27 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136591335</t>
+          <t>https://artportalen.se/Sighting/136585518</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>136591338</v>
+        <v>136585522</v>
       </c>
       <c r="B42" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5218,14 +5254,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Liejbebákte, Tellejokk, S Jokkmokk, Lu lm</t>
+          <t>Liejbebákte, Lu lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>714644</v>
+        <v>714681</v>
       </c>
       <c r="R42" t="n">
-        <v>7335224</v>
+        <v>7335197</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5257,7 +5293,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5267,7 +5303,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5282,27 +5318,27 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136591338</t>
+          <t>https://artportalen.se/Sighting/136585522</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>136591345</v>
+        <v>136585527</v>
       </c>
       <c r="B43" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5327,28 +5363,17 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Liejbebákte, Tellejokk, S Jokkmokk, Lu lm</t>
+          <t>Liejbebákte, Lu lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>714693</v>
+        <v>714655</v>
       </c>
       <c r="R43" t="n">
-        <v>7335053</v>
+        <v>7334958</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5380,7 +5405,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5390,12 +5415,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>14 st i häxring</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5404,34 +5424,33 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136591345</t>
+          <t>https://artportalen.se/Sighting/136585527</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>136591354</v>
+        <v>136591316</v>
       </c>
       <c r="B44" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5463,10 +5482,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>714654</v>
+        <v>714539</v>
       </c>
       <c r="R44" t="n">
-        <v>7334835</v>
+        <v>7335184</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5498,7 +5517,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5508,7 +5527,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5534,58 +5553,54 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136591354</t>
+          <t>https://artportalen.se/Sighting/136591316</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129000557</v>
+        <v>136591335</v>
       </c>
       <c r="B45" t="n">
-        <v>93201</v>
+        <v>93411</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Tellejåkk, Lu lm</t>
+          <t>Liejbebákte, Tellejokk, S Jokkmokk, Lu lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>714683</v>
+        <v>714653</v>
       </c>
       <c r="R45" t="n">
-        <v>7335256</v>
+        <v>7335255</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5609,17 +5624,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5634,62 +5654,62 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000557</t>
+          <t>https://artportalen.se/Sighting/136591335</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>136585489</v>
+        <v>136591338</v>
       </c>
       <c r="B46" t="n">
-        <v>93413</v>
+        <v>93411</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Liejbebákte, Lu lm</t>
+          <t>Liejbebákte, Tellejokk, S Jokkmokk, Lu lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>714674</v>
+        <v>714644</v>
       </c>
       <c r="R46" t="n">
-        <v>7334962</v>
+        <v>7335224</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5721,7 +5741,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5731,7 +5751,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5746,62 +5766,73 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136585489</t>
+          <t>https://artportalen.se/Sighting/136591338</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>136591295</v>
+        <v>136591345</v>
       </c>
       <c r="B47" t="n">
-        <v>93413</v>
+        <v>93411</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Liejbebákte, Tellejokk, S Jokkmokk, Lu lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>714678</v>
+        <v>714693</v>
       </c>
       <c r="R47" t="n">
-        <v>7334983</v>
+        <v>7335053</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5833,7 +5864,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5843,7 +5874,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>14 st i häxring</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5852,6 +5888,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5869,38 +5906,38 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136591295</t>
+          <t>https://artportalen.se/Sighting/136591345</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>136591314</v>
+        <v>136591354</v>
       </c>
       <c r="B48" t="n">
-        <v>93413</v>
+        <v>93411</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5910,10 +5947,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>714553</v>
+        <v>714654</v>
       </c>
       <c r="R48" t="n">
-        <v>7335172</v>
+        <v>7334835</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5945,7 +5982,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5955,7 +5992,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5981,51 +6018,55 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136591314</t>
+          <t>https://artportalen.se/Sighting/136591354</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>136591339</v>
+        <v>136858053</v>
       </c>
       <c r="B49" t="n">
-        <v>93413</v>
+        <v>93411</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Liejbebákte, Tellejokk, S Jokkmokk, Lu lm</t>
+          <t>Tellejåkk, Lu lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>714640</v>
+        <v>714508</v>
       </c>
       <c r="R49" t="n">
-        <v>7335225</v>
+        <v>7335014</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6052,22 +6093,27 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6082,27 +6128,27 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136591339</t>
+          <t>https://artportalen.se/Sighting/136858053</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129000551</v>
+        <v>136858054</v>
       </c>
       <c r="B50" t="n">
-        <v>93209</v>
+        <v>93411</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6110,21 +6156,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -6138,13 +6184,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>714545</v>
+        <v>714536</v>
       </c>
       <c r="R50" t="n">
-        <v>7335167</v>
+        <v>7335040</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6168,12 +6214,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
@@ -6204,16 +6260,16 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000551</t>
+          <t>https://artportalen.se/Sighting/136858054</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129000559</v>
+        <v>136858055</v>
       </c>
       <c r="B51" t="n">
-        <v>93209</v>
+        <v>93411</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6221,21 +6277,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -6249,13 +6305,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>714667</v>
+        <v>714498</v>
       </c>
       <c r="R51" t="n">
-        <v>7334870</v>
+        <v>7335093</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6279,12 +6335,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
@@ -6315,54 +6381,58 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000559</t>
+          <t>https://artportalen.se/Sighting/136858055</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>136591297</v>
+        <v>129000557</v>
       </c>
       <c r="B52" t="n">
-        <v>93053</v>
+        <v>93201</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4745</v>
+        <v>4365</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Fr.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Liejbebákte, Tellejokk, S Jokkmokk, Lu lm</t>
+          <t>Tellejåkk, Lu lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>714659</v>
+        <v>714683</v>
       </c>
       <c r="R52" t="n">
-        <v>7335009</v>
+        <v>7335256</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6386,22 +6456,17 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>12:01</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>12:01</t>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6416,62 +6481,62 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136591297</t>
+          <t>https://artportalen.se/Sighting/129000557</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>136591303</v>
+        <v>136585489</v>
       </c>
       <c r="B53" t="n">
-        <v>93053</v>
+        <v>93415</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4745</v>
+        <v>4365</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Liejbebákte, Tellejokk, S Jokkmokk, Lu lm</t>
+          <t>Liejbebákte, Lu lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>714626</v>
+        <v>714674</v>
       </c>
       <c r="R53" t="n">
-        <v>7335048</v>
+        <v>7334962</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6503,7 +6568,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6513,7 +6578,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6528,49 +6593,49 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136591303</t>
+          <t>https://artportalen.se/Sighting/136585489</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>136591307</v>
+        <v>136591295</v>
       </c>
       <c r="B54" t="n">
-        <v>93053</v>
+        <v>93415</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4745</v>
+        <v>4365</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6580,10 +6645,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>714655</v>
+        <v>714678</v>
       </c>
       <c r="R54" t="n">
-        <v>7335063</v>
+        <v>7334983</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6615,7 +6680,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6625,7 +6690,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6651,51 +6716,51 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136591307</t>
+          <t>https://artportalen.se/Sighting/136591295</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>136585526</v>
+        <v>136591314</v>
       </c>
       <c r="B55" t="n">
-        <v>93435</v>
+        <v>93415</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5448</v>
+        <v>4365</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Liejbebákte, Lu lm</t>
+          <t>Liejbebákte, Tellejokk, S Jokkmokk, Lu lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>714710</v>
+        <v>714553</v>
       </c>
       <c r="R55" t="n">
-        <v>7335020</v>
+        <v>7335172</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6727,7 +6792,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6737,7 +6802,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6752,65 +6817,65 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136585526</t>
+          <t>https://artportalen.se/Sighting/136591314</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>136585493</v>
+        <v>136591339</v>
       </c>
       <c r="B56" t="n">
-        <v>78879</v>
+        <v>93415</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6437</v>
+        <v>4365</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Liejbebákte, Lu lm</t>
+          <t>Liejbebákte, Tellejokk, S Jokkmokk, Lu lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>714646</v>
+        <v>714640</v>
       </c>
       <c r="R56" t="n">
-        <v>7335029</v>
+        <v>7335225</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6839,7 +6904,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6849,7 +6914,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6864,27 +6929,27 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136585493</t>
+          <t>https://artportalen.se/Sighting/136591339</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>136585494</v>
+        <v>129000551</v>
       </c>
       <c r="B57" t="n">
-        <v>78879</v>
+        <v>93209</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6892,37 +6957,41 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6437</v>
+        <v>4366</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Liejbebákte, Lu lm</t>
+          <t>Tellejåkk, Lu lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>714635</v>
+        <v>714545</v>
       </c>
       <c r="R57" t="n">
-        <v>7335010</v>
+        <v>7335167</v>
       </c>
       <c r="S57" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6946,22 +7015,17 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>12:17</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>12:17</t>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6976,27 +7040,27 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136585494</t>
+          <t>https://artportalen.se/Sighting/129000551</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>136585520</v>
+        <v>129000559</v>
       </c>
       <c r="B58" t="n">
-        <v>78879</v>
+        <v>93209</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7004,37 +7068,41 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6437</v>
+        <v>4366</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Liejbebákte, Lu lm</t>
+          <t>Tellejåkk, Lu lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>714664</v>
+        <v>714667</v>
       </c>
       <c r="R58" t="n">
-        <v>7335211</v>
+        <v>7334870</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7058,22 +7126,17 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>16:09</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>16:09</t>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7088,27 +7151,27 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136585520</t>
+          <t>https://artportalen.se/Sighting/129000559</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>136591289</v>
+        <v>136591297</v>
       </c>
       <c r="B59" t="n">
-        <v>78879</v>
+        <v>93055</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7116,21 +7179,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6437</v>
+        <v>4745</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7140,10 +7203,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>714679</v>
+        <v>714659</v>
       </c>
       <c r="R59" t="n">
-        <v>7334903</v>
+        <v>7335009</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7175,7 +7238,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7185,7 +7248,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7211,16 +7274,16 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136591289</t>
+          <t>https://artportalen.se/Sighting/136591297</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>136591292</v>
+        <v>136591303</v>
       </c>
       <c r="B60" t="n">
-        <v>78879</v>
+        <v>93055</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7228,21 +7291,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6437</v>
+        <v>4745</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7252,10 +7315,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>714697</v>
+        <v>714626</v>
       </c>
       <c r="R60" t="n">
-        <v>7334942</v>
+        <v>7335048</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7287,7 +7350,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7297,7 +7360,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7323,16 +7386,16 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136591292</t>
+          <t>https://artportalen.se/Sighting/136591303</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>136591299</v>
+        <v>136591307</v>
       </c>
       <c r="B61" t="n">
-        <v>78879</v>
+        <v>93055</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7340,21 +7403,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6437</v>
+        <v>4745</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7364,10 +7427,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>714658</v>
+        <v>714655</v>
       </c>
       <c r="R61" t="n">
-        <v>7335015</v>
+        <v>7335063</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7399,7 +7462,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7409,7 +7472,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7435,16 +7498,16 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136591299</t>
+          <t>https://artportalen.se/Sighting/136591307</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>136591305</v>
+        <v>136585526</v>
       </c>
       <c r="B62" t="n">
-        <v>78879</v>
+        <v>93437</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7452,34 +7515,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6437</v>
+        <v>5448</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Liejbebákte, Tellejokk, S Jokkmokk, Lu lm</t>
+          <t>Liejbebákte, Lu lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>714648</v>
+        <v>714710</v>
       </c>
       <c r="R62" t="n">
-        <v>7335041</v>
+        <v>7335020</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7511,7 +7574,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7521,7 +7584,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7536,24 +7599,24 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136591305</t>
+          <t>https://artportalen.se/Sighting/136585526</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>136591308</v>
+        <v>136585493</v>
       </c>
       <c r="B63" t="n">
         <v>78879</v>
@@ -7584,17 +7647,17 @@
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Liejbebákte, Tellejokk, S Jokkmokk, Lu lm</t>
+          <t>Liejbebákte, Lu lm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>714658</v>
+        <v>714646</v>
       </c>
       <c r="R63" t="n">
-        <v>7335079</v>
+        <v>7335029</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7623,7 +7686,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7633,7 +7696,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7648,24 +7711,24 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136591308</t>
+          <t>https://artportalen.se/Sighting/136585493</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>136591312</v>
+        <v>136585494</v>
       </c>
       <c r="B64" t="n">
         <v>78879</v>
@@ -7696,17 +7759,17 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Liejbebákte, Tellejokk, S Jokkmokk, Lu lm</t>
+          <t>Liejbebákte, Lu lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>714563</v>
+        <v>714635</v>
       </c>
       <c r="R64" t="n">
-        <v>7335148</v>
+        <v>7335010</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7735,7 +7798,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7745,7 +7808,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7760,24 +7823,24 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136591312</t>
+          <t>https://artportalen.se/Sighting/136585494</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>136591318</v>
+        <v>136585520</v>
       </c>
       <c r="B65" t="n">
         <v>78879</v>
@@ -7808,14 +7871,14 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Liejbebákte, Tellejokk, S Jokkmokk, Lu lm</t>
+          <t>Liejbebákte, Lu lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>714533</v>
+        <v>714664</v>
       </c>
       <c r="R65" t="n">
-        <v>7335198</v>
+        <v>7335211</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7847,7 +7910,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7857,7 +7920,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7872,24 +7935,24 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136591318</t>
+          <t>https://artportalen.se/Sighting/136585520</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>136591322</v>
+        <v>136591289</v>
       </c>
       <c r="B66" t="n">
         <v>78879</v>
@@ -7924,10 +7987,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>714565</v>
+        <v>714679</v>
       </c>
       <c r="R66" t="n">
-        <v>7335273</v>
+        <v>7334903</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7959,7 +8022,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7969,7 +8032,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7995,13 +8058,13 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136591322</t>
+          <t>https://artportalen.se/Sighting/136591289</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>136591325</v>
+        <v>136591292</v>
       </c>
       <c r="B67" t="n">
         <v>78879</v>
@@ -8036,10 +8099,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>714589</v>
+        <v>714697</v>
       </c>
       <c r="R67" t="n">
-        <v>7335255</v>
+        <v>7334942</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -8071,7 +8134,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8081,7 +8144,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8107,13 +8170,13 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136591325</t>
+          <t>https://artportalen.se/Sighting/136591292</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>136591332</v>
+        <v>136591299</v>
       </c>
       <c r="B68" t="n">
         <v>78879</v>
@@ -8148,10 +8211,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>714632</v>
+        <v>714658</v>
       </c>
       <c r="R68" t="n">
-        <v>7335277</v>
+        <v>7335015</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8183,7 +8246,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8193,7 +8256,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8219,13 +8282,13 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136591332</t>
+          <t>https://artportalen.se/Sighting/136591299</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>136591337</v>
+        <v>136591305</v>
       </c>
       <c r="B69" t="n">
         <v>78879</v>
@@ -8260,10 +8323,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>714670</v>
+        <v>714648</v>
       </c>
       <c r="R69" t="n">
-        <v>7335226</v>
+        <v>7335041</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8295,7 +8358,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8305,7 +8368,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8331,13 +8394,13 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136591337</t>
+          <t>https://artportalen.se/Sighting/136591305</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>136591342</v>
+        <v>136591308</v>
       </c>
       <c r="B70" t="n">
         <v>78879</v>
@@ -8372,10 +8435,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>714636</v>
+        <v>714658</v>
       </c>
       <c r="R70" t="n">
-        <v>7335195</v>
+        <v>7335079</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8407,7 +8470,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8417,7 +8480,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8443,13 +8506,13 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136591342</t>
+          <t>https://artportalen.se/Sighting/136591308</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>136591348</v>
+        <v>136591312</v>
       </c>
       <c r="B71" t="n">
         <v>78879</v>
@@ -8484,10 +8547,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>714610</v>
+        <v>714563</v>
       </c>
       <c r="R71" t="n">
-        <v>7334953</v>
+        <v>7335148</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8519,7 +8582,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8529,7 +8592,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8555,13 +8618,13 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136591348</t>
+          <t>https://artportalen.se/Sighting/136591312</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>136591352</v>
+        <v>136591318</v>
       </c>
       <c r="B72" t="n">
         <v>78879</v>
@@ -8596,10 +8659,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>714574</v>
+        <v>714533</v>
       </c>
       <c r="R72" t="n">
-        <v>7334806</v>
+        <v>7335198</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8631,7 +8694,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8641,7 +8704,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8667,16 +8730,16 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136591352</t>
+          <t>https://artportalen.se/Sighting/136591318</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129000552</v>
+        <v>136591322</v>
       </c>
       <c r="B73" t="n">
-        <v>79084</v>
+        <v>78879</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8684,41 +8747,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Tellejåkk, Lu lm</t>
+          <t>Liejbebákte, Tellejokk, S Jokkmokk, Lu lm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>714562</v>
+        <v>714565</v>
       </c>
       <c r="R73" t="n">
-        <v>7335193</v>
+        <v>7335273</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8742,17 +8801,22 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8767,27 +8831,27 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000552</t>
+          <t>https://artportalen.se/Sighting/136591322</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129000558</v>
+        <v>136591325</v>
       </c>
       <c r="B74" t="n">
-        <v>79084</v>
+        <v>78879</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8795,41 +8859,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Tellejåkk, Lu lm</t>
+          <t>Liejbebákte, Tellejokk, S Jokkmokk, Lu lm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>714644</v>
+        <v>714589</v>
       </c>
       <c r="R74" t="n">
-        <v>7334911</v>
+        <v>7335255</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8853,17 +8913,22 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8878,27 +8943,27 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000558</t>
+          <t>https://artportalen.se/Sighting/136591325</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>136585487</v>
+        <v>136591332</v>
       </c>
       <c r="B75" t="n">
-        <v>79233</v>
+        <v>78879</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8906,37 +8971,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Liejbebákte, Lu lm</t>
+          <t>Liejbebákte, Tellejokk, S Jokkmokk, Lu lm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>714693</v>
+        <v>714632</v>
       </c>
       <c r="R75" t="n">
-        <v>7334944</v>
+        <v>7335277</v>
       </c>
       <c r="S75" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8965,7 +9030,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8975,7 +9040,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8990,27 +9055,27 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136585487</t>
+          <t>https://artportalen.se/Sighting/136591332</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>136585524</v>
+        <v>136591337</v>
       </c>
       <c r="B76" t="n">
-        <v>79233</v>
+        <v>78879</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9018,34 +9083,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Liejbebákte, Lu lm</t>
+          <t>Liejbebákte, Tellejokk, S Jokkmokk, Lu lm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>714682</v>
+        <v>714670</v>
       </c>
       <c r="R76" t="n">
-        <v>7335100</v>
+        <v>7335226</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -9077,7 +9142,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9087,7 +9152,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9096,34 +9161,33 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136585524</t>
+          <t>https://artportalen.se/Sighting/136591337</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>136591288</v>
+        <v>136591342</v>
       </c>
       <c r="B77" t="n">
-        <v>79233</v>
+        <v>78879</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9131,21 +9195,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9155,10 +9219,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>714678</v>
+        <v>714636</v>
       </c>
       <c r="R77" t="n">
-        <v>7334889</v>
+        <v>7335195</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9190,7 +9254,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9200,7 +9264,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9226,16 +9290,16 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136591288</t>
+          <t>https://artportalen.se/Sighting/136591342</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>136591300</v>
+        <v>136591348</v>
       </c>
       <c r="B78" t="n">
-        <v>79233</v>
+        <v>78879</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9243,21 +9307,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9267,10 +9331,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>714656</v>
+        <v>714610</v>
       </c>
       <c r="R78" t="n">
-        <v>7335014</v>
+        <v>7334953</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9302,7 +9366,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9312,7 +9376,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9338,16 +9402,16 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136591300</t>
+          <t>https://artportalen.se/Sighting/136591348</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>136585513</v>
+        <v>136591352</v>
       </c>
       <c r="B79" t="n">
-        <v>80095</v>
+        <v>78879</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9355,37 +9419,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Liejbebákte, Lu lm</t>
+          <t>Liejbebákte, Tellejokk, S Jokkmokk, Lu lm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>714552</v>
+        <v>714574</v>
       </c>
       <c r="R79" t="n">
-        <v>7335124</v>
+        <v>7334806</v>
       </c>
       <c r="S79" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9414,7 +9478,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9424,7 +9488,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9439,27 +9503,27 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136585513</t>
+          <t>https://artportalen.se/Sighting/136591352</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>136585515</v>
+        <v>129000552</v>
       </c>
       <c r="B80" t="n">
-        <v>80095</v>
+        <v>79084</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9467,37 +9531,41 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Liejbebákte, Lu lm</t>
+          <t>Tellejåkk, Lu lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>714526</v>
+        <v>714562</v>
       </c>
       <c r="R80" t="n">
-        <v>7335207</v>
+        <v>7335193</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9521,22 +9589,17 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>14:35</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>14:35</t>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9551,27 +9614,27 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136585515</t>
+          <t>https://artportalen.se/Sighting/129000552</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>136591344</v>
+        <v>129000558</v>
       </c>
       <c r="B81" t="n">
-        <v>80095</v>
+        <v>79084</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9579,37 +9642,41 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Liejbebákte, Tellejokk, S Jokkmokk, Lu lm</t>
+          <t>Tellejåkk, Lu lm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>714710</v>
+        <v>714644</v>
       </c>
       <c r="R81" t="n">
-        <v>7335115</v>
+        <v>7334911</v>
       </c>
       <c r="S81" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9633,22 +9700,17 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>16:25</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>16:25</t>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9663,27 +9725,27 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136591344</t>
+          <t>https://artportalen.se/Sighting/129000558</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>136591309</v>
+        <v>136585487</v>
       </c>
       <c r="B82" t="n">
-        <v>78480</v>
+        <v>79233</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9691,37 +9753,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6487</v>
+        <v>6446</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Liejbebákte, Tellejokk, S Jokkmokk, Lu lm</t>
+          <t>Liejbebákte, Lu lm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>714627</v>
+        <v>714693</v>
       </c>
       <c r="R82" t="n">
-        <v>7335061</v>
+        <v>7334944</v>
       </c>
       <c r="S82" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9750,7 +9812,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9760,7 +9822,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9775,27 +9837,27 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136591309</t>
+          <t>https://artportalen.se/Sighting/136585487</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>136591323</v>
+        <v>136585524</v>
       </c>
       <c r="B83" t="n">
-        <v>78480</v>
+        <v>79233</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9803,34 +9865,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6487</v>
+        <v>6446</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Liejbebákte, Tellejokk, S Jokkmokk, Lu lm</t>
+          <t>Liejbebákte, Lu lm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>714550</v>
+        <v>714682</v>
       </c>
       <c r="R83" t="n">
-        <v>7335268</v>
+        <v>7335100</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9862,7 +9924,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9872,7 +9934,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9881,76 +9943,69 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136591323</t>
+          <t>https://artportalen.se/Sighting/136585524</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>136591343</v>
+        <v>136591288</v>
       </c>
       <c r="B84" t="n">
-        <v>57195</v>
+        <v>79233</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Liejbebákte, Tellejokk, S Jokkmokk, Lu lm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>714694</v>
+        <v>714678</v>
       </c>
       <c r="R84" t="n">
-        <v>7335154</v>
+        <v>7334889</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9982,7 +10037,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9992,7 +10047,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10018,16 +10073,16 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136591343</t>
+          <t>https://artportalen.se/Sighting/136591288</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>136591304</v>
+        <v>136591300</v>
       </c>
       <c r="B85" t="n">
-        <v>58112</v>
+        <v>79233</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10035,42 +10090,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>103031</v>
+        <v>6446</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Liejbebákte, Tellejokk, S Jokkmokk, Lu lm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>714625</v>
+        <v>714656</v>
       </c>
       <c r="R85" t="n">
-        <v>7335033</v>
+        <v>7335014</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -10102,7 +10149,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10112,7 +10159,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10138,16 +10185,16 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136591304</t>
+          <t>https://artportalen.se/Sighting/136591300</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>136585501</v>
+        <v>136585513</v>
       </c>
       <c r="B86" t="n">
-        <v>79234</v>
+        <v>80095</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10155,21 +10202,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10179,13 +10226,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>714633</v>
+        <v>714552</v>
       </c>
       <c r="R86" t="n">
-        <v>7335062</v>
+        <v>7335124</v>
       </c>
       <c r="S86" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10214,7 +10261,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10224,7 +10271,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10250,16 +10297,16 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136585501</t>
+          <t>https://artportalen.se/Sighting/136585513</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>136585512</v>
+        <v>136585515</v>
       </c>
       <c r="B87" t="n">
-        <v>79234</v>
+        <v>80095</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10267,21 +10314,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10291,10 +10338,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>714560</v>
+        <v>714526</v>
       </c>
       <c r="R87" t="n">
-        <v>7335136</v>
+        <v>7335206</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -10326,7 +10373,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10336,7 +10383,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10362,16 +10409,16 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136585512</t>
+          <t>https://artportalen.se/Sighting/136585515</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>136585523</v>
+        <v>136591344</v>
       </c>
       <c r="B88" t="n">
-        <v>79234</v>
+        <v>80095</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10379,34 +10426,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Liejbebákte, Lu lm</t>
+          <t>Liejbebákte, Tellejokk, S Jokkmokk, Lu lm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>714681</v>
+        <v>714710</v>
       </c>
       <c r="R88" t="n">
-        <v>7335099</v>
+        <v>7335115</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -10438,7 +10485,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10448,7 +10495,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10463,27 +10510,27 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136585523</t>
+          <t>https://artportalen.se/Sighting/136591344</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>136585529</v>
+        <v>136591309</v>
       </c>
       <c r="B89" t="n">
-        <v>79234</v>
+        <v>78480</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10491,37 +10538,37 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Liejbebákte, Lu lm</t>
+          <t>Liejbebákte, Tellejokk, S Jokkmokk, Lu lm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>714556</v>
+        <v>714627</v>
       </c>
       <c r="R89" t="n">
-        <v>7334948</v>
+        <v>7335061</v>
       </c>
       <c r="S89" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10550,7 +10597,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10560,7 +10607,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10575,27 +10622,27 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136585529</t>
+          <t>https://artportalen.se/Sighting/136591309</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>136585532</v>
+        <v>136591323</v>
       </c>
       <c r="B90" t="n">
-        <v>79234</v>
+        <v>78480</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10603,34 +10650,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Liejbebákte, Lu lm</t>
+          <t>Liejbebákte, Tellejokk, S Jokkmokk, Lu lm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>714588</v>
+        <v>714550</v>
       </c>
       <c r="R90" t="n">
-        <v>7334778</v>
+        <v>7335268</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10662,7 +10709,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10672,7 +10719,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10687,62 +10734,70 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136585532</t>
+          <t>https://artportalen.se/Sighting/136591323</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>136591287</v>
+        <v>136591343</v>
       </c>
       <c r="B91" t="n">
-        <v>79234</v>
+        <v>57195</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Liejbebákte, Tellejokk, S Jokkmokk, Lu lm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>714678</v>
+        <v>714694</v>
       </c>
       <c r="R91" t="n">
-        <v>7334889</v>
+        <v>7335154</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10774,7 +10829,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10784,7 +10839,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10810,16 +10865,16 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136591287</t>
+          <t>https://artportalen.se/Sighting/136591343</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>136591306</v>
+        <v>136591304</v>
       </c>
       <c r="B92" t="n">
-        <v>79234</v>
+        <v>58112</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10827,34 +10882,42 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>228912</v>
+        <v>103031</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Liejbebákte, Tellejokk, S Jokkmokk, Lu lm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>714651</v>
+        <v>714625</v>
       </c>
       <c r="R92" t="n">
-        <v>7335047</v>
+        <v>7335033</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10886,7 +10949,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10896,7 +10959,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10922,13 +10985,13 @@
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136591306</t>
+          <t>https://artportalen.se/Sighting/136591304</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>136591311</v>
+        <v>136585501</v>
       </c>
       <c r="B93" t="n">
         <v>79234</v>
@@ -10959,14 +11022,14 @@
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Liejbebákte, Tellejokk, S Jokkmokk, Lu lm</t>
+          <t>Liejbebákte, Lu lm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>714576</v>
+        <v>714633</v>
       </c>
       <c r="R93" t="n">
-        <v>7335130</v>
+        <v>7335062</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10998,7 +11061,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11008,7 +11071,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11023,24 +11086,24 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136591311</t>
+          <t>https://artportalen.se/Sighting/136585501</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>136591317</v>
+        <v>136585512</v>
       </c>
       <c r="B94" t="n">
         <v>79234</v>
@@ -11071,14 +11134,14 @@
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Liejbebákte, Tellejokk, S Jokkmokk, Lu lm</t>
+          <t>Liejbebákte, Lu lm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>714539</v>
+        <v>714560</v>
       </c>
       <c r="R94" t="n">
-        <v>7335188</v>
+        <v>7335136</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -11110,7 +11173,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11120,7 +11183,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11135,24 +11198,24 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136591317</t>
+          <t>https://artportalen.se/Sighting/136585512</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>136591324</v>
+        <v>136585523</v>
       </c>
       <c r="B95" t="n">
         <v>79234</v>
@@ -11183,14 +11246,14 @@
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Liejbebákte, Tellejokk, S Jokkmokk, Lu lm</t>
+          <t>Liejbebákte, Lu lm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>714573</v>
+        <v>714681</v>
       </c>
       <c r="R95" t="n">
-        <v>7335271</v>
+        <v>7335099</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -11222,7 +11285,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11232,7 +11295,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11247,24 +11310,24 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136591324</t>
+          <t>https://artportalen.se/Sighting/136585523</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>136591350</v>
+        <v>136585529</v>
       </c>
       <c r="B96" t="n">
         <v>79234</v>
@@ -11295,14 +11358,14 @@
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Liejbebákte, Tellejokk, S Jokkmokk, Lu lm</t>
+          <t>Liejbebákte, Lu lm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>714561</v>
+        <v>714556</v>
       </c>
       <c r="R96" t="n">
-        <v>7334956</v>
+        <v>7334948</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -11334,7 +11397,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11344,7 +11407,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11359,24 +11422,24 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136591350</t>
+          <t>https://artportalen.se/Sighting/136585529</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>136591353</v>
+        <v>136585532</v>
       </c>
       <c r="B97" t="n">
         <v>79234</v>
@@ -11407,14 +11470,14 @@
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Liejbebákte, Tellejokk, S Jokkmokk, Lu lm</t>
+          <t>Liejbebákte, Lu lm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>714646</v>
+        <v>714588</v>
       </c>
       <c r="R97" t="n">
-        <v>7334816</v>
+        <v>7334778</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -11446,7 +11509,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11456,7 +11519,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11471,24 +11534,24 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136591353</t>
+          <t>https://artportalen.se/Sighting/136585532</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>136591355</v>
+        <v>136591287</v>
       </c>
       <c r="B98" t="n">
         <v>79234</v>
@@ -11523,7 +11586,7 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>714680</v>
+        <v>714678</v>
       </c>
       <c r="R98" t="n">
         <v>7334889</v>
@@ -11558,7 +11621,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11568,7 +11631,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11594,16 +11657,16 @@
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136591355</t>
+          <t>https://artportalen.se/Sighting/136591287</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129000553</v>
+        <v>136591306</v>
       </c>
       <c r="B99" t="n">
-        <v>79917</v>
+        <v>79234</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11611,41 +11674,37 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Tellejåkk, Lu lm</t>
+          <t>Liejbebákte, Tellejokk, S Jokkmokk, Lu lm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>714631</v>
+        <v>714651</v>
       </c>
       <c r="R99" t="n">
-        <v>7335301</v>
+        <v>7335047</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11669,17 +11728,22 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11694,27 +11758,27 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000553</t>
+          <t>https://artportalen.se/Sighting/136591306</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>136591301</v>
+        <v>136591311</v>
       </c>
       <c r="B100" t="n">
-        <v>80066</v>
+        <v>79234</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11722,21 +11786,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11746,10 +11810,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>714645</v>
+        <v>714576</v>
       </c>
       <c r="R100" t="n">
-        <v>7335024</v>
+        <v>7335130</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -11781,7 +11845,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11791,7 +11855,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11817,58 +11881,54 @@
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136591301</t>
+          <t>https://artportalen.se/Sighting/136591311</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129000554</v>
+        <v>136591317</v>
       </c>
       <c r="B101" t="n">
-        <v>93228</v>
+        <v>79234</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>232140</v>
+        <v>228912</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Tellejåkk, Lu lm</t>
+          <t>Liejbebákte, Tellejokk, S Jokkmokk, Lu lm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>714704</v>
+        <v>714539</v>
       </c>
       <c r="R101" t="n">
-        <v>7335293</v>
+        <v>7335188</v>
       </c>
       <c r="S101" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11892,17 +11952,22 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11917,73 +11982,62 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000554</t>
+          <t>https://artportalen.se/Sighting/136591317</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>136591313</v>
+        <v>136591324</v>
       </c>
       <c r="B102" t="n">
-        <v>93440</v>
+        <v>79234</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>232140</v>
+        <v>228912</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Liejbebákte, Tellejokk, S Jokkmokk, Lu lm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>714552</v>
+        <v>714573</v>
       </c>
       <c r="R102" t="n">
-        <v>7335166</v>
+        <v>7335271</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -12015,7 +12069,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12025,16 +12079,15 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD102" t="b">
         <v>0</v>
       </c>
       <c r="AE102" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF102" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -12052,54 +12105,51 @@
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136591313</t>
+          <t>https://artportalen.se/Sighting/136591324</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>136591334</v>
+        <v>136591350</v>
       </c>
       <c r="B103" t="n">
-        <v>93440</v>
+        <v>79234</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>232140</v>
+        <v>228912</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Liejbebákte, Tellejokk, S Jokkmokk, Lu lm</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>714652</v>
+        <v>714561</v>
       </c>
       <c r="R103" t="n">
-        <v>7335276</v>
+        <v>7334956</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -12131,7 +12181,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12141,21 +12191,15 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>15:22</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>Kände ingen buljong eller selleridoft</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD103" t="b">
         <v>0</v>
       </c>
       <c r="AE103" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF103" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
@@ -12173,16 +12217,16 @@
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136591334</t>
+          <t>https://artportalen.se/Sighting/136591350</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>136591294</v>
+        <v>136591353</v>
       </c>
       <c r="B104" t="n">
-        <v>79499</v>
+        <v>79234</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12190,21 +12234,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>260591</v>
+        <v>228912</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -12214,10 +12258,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>714691</v>
+        <v>714646</v>
       </c>
       <c r="R104" t="n">
-        <v>7334970</v>
+        <v>7334816</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -12249,7 +12293,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12259,7 +12303,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12285,16 +12329,16 @@
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136591294</t>
+          <t>https://artportalen.se/Sighting/136591353</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>136591321</v>
+        <v>136591355</v>
       </c>
       <c r="B105" t="n">
-        <v>79499</v>
+        <v>79234</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12302,41 +12346,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>260591</v>
+        <v>228912</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Liejbebákte, Tellejokk, S Jokkmokk, Lu lm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>714546</v>
+        <v>714680</v>
       </c>
       <c r="R105" t="n">
-        <v>7335275</v>
+        <v>7334889</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -12368,7 +12405,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12378,12 +12415,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>14:46</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Med gul soral</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12392,7 +12424,6 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
@@ -12410,16 +12441,16 @@
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136591321</t>
+          <t>https://artportalen.se/Sighting/136591355</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>136591341</v>
+        <v>129000553</v>
       </c>
       <c r="B106" t="n">
-        <v>79499</v>
+        <v>79917</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12427,37 +12458,41 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>260591</v>
+        <v>229821</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr"/>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Liejbebákte, Tellejokk, S Jokkmokk, Lu lm</t>
+          <t>Tellejåkk, Lu lm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>714637</v>
+        <v>714631</v>
       </c>
       <c r="R106" t="n">
-        <v>7335214</v>
+        <v>7335301</v>
       </c>
       <c r="S106" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12481,22 +12516,17 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="Z106" t="inlineStr">
-        <is>
-          <t>16:14</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="AB106" t="inlineStr">
-        <is>
-          <t>16:14</t>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12511,16 +12541,954 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000553</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>136591301</v>
+      </c>
+      <c r="B107" t="n">
+        <v>80066</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Liejbebákte, Tellejokk, S Jokkmokk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>714645</v>
+      </c>
+      <c r="R107" t="n">
+        <v>7335024</v>
+      </c>
+      <c r="S107" t="n">
+        <v>5</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136591301</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>129000554</v>
+      </c>
+      <c r="B108" t="n">
+        <v>93228</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>232140</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Tajgataggsvamp</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Phellodon secretus</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Tellejåkk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>714704</v>
+      </c>
+      <c r="R108" t="n">
+        <v>7335293</v>
+      </c>
+      <c r="S108" t="n">
+        <v>10</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000554</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>136591313</v>
+      </c>
+      <c r="B109" t="n">
+        <v>93442</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>232140</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Tajgataggsvamp</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Phellodon secretus</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Liejbebákte, Tellejokk, S Jokkmokk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>714552</v>
+      </c>
+      <c r="R109" t="n">
+        <v>7335166</v>
+      </c>
+      <c r="S109" t="n">
+        <v>5</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF109" t="inlineStr"/>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136591313</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>136591334</v>
+      </c>
+      <c r="B110" t="n">
+        <v>93442</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>232140</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Tajgataggsvamp</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Phellodon secretus</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Liejbebákte, Tellejokk, S Jokkmokk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>714652</v>
+      </c>
+      <c r="R110" t="n">
+        <v>7335276</v>
+      </c>
+      <c r="S110" t="n">
+        <v>5</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Kände ingen buljong eller selleridoft</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF110" t="inlineStr"/>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136591334</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>136857936</v>
+      </c>
+      <c r="B111" t="n">
+        <v>93442</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>232140</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Tajgataggsvamp</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Phellodon secretus</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Tellejåkk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>714549</v>
+      </c>
+      <c r="R111" t="n">
+        <v>7334987</v>
+      </c>
+      <c r="S111" t="n">
+        <v>5</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136857936</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>136591294</v>
+      </c>
+      <c r="B112" t="n">
+        <v>79499</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Liejbebákte, Tellejokk, S Jokkmokk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>714691</v>
+      </c>
+      <c r="R112" t="n">
+        <v>7334970</v>
+      </c>
+      <c r="S112" t="n">
+        <v>5</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136591294</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>136591321</v>
+      </c>
+      <c r="B113" t="n">
+        <v>79499</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Liejbebákte, Tellejokk, S Jokkmokk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>714546</v>
+      </c>
+      <c r="R113" t="n">
+        <v>7335275</v>
+      </c>
+      <c r="S113" t="n">
+        <v>5</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>Med gul soral</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF113" t="inlineStr"/>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136591321</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>136591341</v>
+      </c>
+      <c r="B114" t="n">
+        <v>79499</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Liejbebákte, Tellejokk, S Jokkmokk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>714637</v>
+      </c>
+      <c r="R114" t="n">
+        <v>7335214</v>
+      </c>
+      <c r="S114" t="n">
+        <v>5</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136591341</t>
         </is>
@@ -12633,6 +13601,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32992-2026 artfynd.xlsx
+++ b/artfynd/A 32992-2026 artfynd.xlsx
@@ -1278,7 +1278,7 @@
         <v>714526</v>
       </c>
       <c r="R7" t="n">
-        <v>7335206</v>
+        <v>7335207</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -10341,7 +10341,7 @@
         <v>714526</v>
       </c>
       <c r="R87" t="n">
-        <v>7335206</v>
+        <v>7335207</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>

--- a/artfynd/A 32992-2026 artfynd.xlsx
+++ b/artfynd/A 32992-2026 artfynd.xlsx
@@ -1278,7 +1278,7 @@
         <v>714526</v>
       </c>
       <c r="R7" t="n">
-        <v>7335207</v>
+        <v>7335206</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -10341,7 +10341,7 @@
         <v>714526</v>
       </c>
       <c r="R87" t="n">
-        <v>7335207</v>
+        <v>7335206</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>

--- a/artfynd/A 32992-2026 artfynd.xlsx
+++ b/artfynd/A 32992-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136585485</v>
       </c>
       <c r="B2" t="n">
-        <v>92359</v>
+        <v>92361</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136585503</v>
       </c>
       <c r="B3" t="n">
-        <v>92359</v>
+        <v>92361</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136585525</v>
       </c>
       <c r="B4" t="n">
-        <v>92359</v>
+        <v>92361</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136591351</v>
       </c>
       <c r="B5" t="n">
-        <v>92359</v>
+        <v>92361</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136585531</v>
       </c>
       <c r="B6" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136591319</v>
       </c>
       <c r="B7" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>714526</v>
       </c>
       <c r="R7" t="n">
-        <v>7335206</v>
+        <v>7335207</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1360,7 +1360,7 @@
         <v>136858049</v>
       </c>
       <c r="B8" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>136858050</v>
       </c>
       <c r="B9" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>136857943</v>
       </c>
       <c r="B10" t="n">
-        <v>89375</v>
+        <v>89377</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>136585507</v>
       </c>
       <c r="B11" t="n">
-        <v>92292</v>
+        <v>92294</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>136591291</v>
       </c>
       <c r="B12" t="n">
-        <v>92292</v>
+        <v>92294</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>136585492</v>
       </c>
       <c r="B13" t="n">
-        <v>91117</v>
+        <v>91119</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>136585497</v>
       </c>
       <c r="B14" t="n">
-        <v>91117</v>
+        <v>91119</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         <v>136585498</v>
       </c>
       <c r="B15" t="n">
-        <v>91117</v>
+        <v>91119</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>136585514</v>
       </c>
       <c r="B16" t="n">
-        <v>91117</v>
+        <v>91119</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>136585517</v>
       </c>
       <c r="B17" t="n">
-        <v>91117</v>
+        <v>91119</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>136585528</v>
       </c>
       <c r="B18" t="n">
-        <v>91117</v>
+        <v>91119</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         <v>136585530</v>
       </c>
       <c r="B19" t="n">
-        <v>91117</v>
+        <v>91119</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>136585533</v>
       </c>
       <c r="B20" t="n">
-        <v>91117</v>
+        <v>91119</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>136591293</v>
       </c>
       <c r="B21" t="n">
-        <v>91117</v>
+        <v>91119</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
         <v>136591296</v>
       </c>
       <c r="B22" t="n">
-        <v>91117</v>
+        <v>91119</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>136591302</v>
       </c>
       <c r="B23" t="n">
-        <v>91117</v>
+        <v>91119</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         <v>136591331</v>
       </c>
       <c r="B24" t="n">
-        <v>91117</v>
+        <v>91119</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>136591333</v>
       </c>
       <c r="B25" t="n">
-        <v>91117</v>
+        <v>91119</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         <v>136857931</v>
       </c>
       <c r="B26" t="n">
-        <v>91117</v>
+        <v>91119</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>136591298</v>
       </c>
       <c r="B27" t="n">
-        <v>93427</v>
+        <v>93429</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>136591346</v>
       </c>
       <c r="B28" t="n">
-        <v>93427</v>
+        <v>93429</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3770,7 +3770,7 @@
         <v>136585490</v>
       </c>
       <c r="B29" t="n">
-        <v>92166</v>
+        <v>92168</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>136585499</v>
       </c>
       <c r="B30" t="n">
-        <v>92166</v>
+        <v>92168</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
         <v>136585516</v>
       </c>
       <c r="B31" t="n">
-        <v>92166</v>
+        <v>92168</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         <v>136585521</v>
       </c>
       <c r="B32" t="n">
-        <v>92166</v>
+        <v>92168</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4219,7 +4219,7 @@
         <v>136591340</v>
       </c>
       <c r="B33" t="n">
-        <v>92166</v>
+        <v>92168</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         <v>136585500</v>
       </c>
       <c r="B34" t="n">
-        <v>92035</v>
+        <v>92037</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4443,7 +4443,7 @@
         <v>136585506</v>
       </c>
       <c r="B35" t="n">
-        <v>92035</v>
+        <v>92037</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4666,7 +4666,7 @@
         <v>136585488</v>
       </c>
       <c r="B37" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>136585491</v>
       </c>
       <c r="B38" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         <v>136585495</v>
       </c>
       <c r="B39" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5002,7 +5002,7 @@
         <v>136585509</v>
       </c>
       <c r="B40" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         <v>136585518</v>
       </c>
       <c r="B41" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
         <v>136585522</v>
       </c>
       <c r="B42" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         <v>136585527</v>
       </c>
       <c r="B43" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         <v>136591316</v>
       </c>
       <c r="B44" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5562,7 +5562,7 @@
         <v>136591335</v>
       </c>
       <c r="B45" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5674,7 +5674,7 @@
         <v>136591338</v>
       </c>
       <c r="B46" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
         <v>136591345</v>
       </c>
       <c r="B47" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5915,7 +5915,7 @@
         <v>136591354</v>
       </c>
       <c r="B48" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         <v>136858053</v>
       </c>
       <c r="B49" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
         <v>136858054</v>
       </c>
       <c r="B50" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6269,7 +6269,7 @@
         <v>136858055</v>
       </c>
       <c r="B51" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6501,7 +6501,7 @@
         <v>136585489</v>
       </c>
       <c r="B53" t="n">
-        <v>93415</v>
+        <v>93417</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6613,7 +6613,7 @@
         <v>136591295</v>
       </c>
       <c r="B54" t="n">
-        <v>93415</v>
+        <v>93417</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         <v>136591314</v>
       </c>
       <c r="B55" t="n">
-        <v>93415</v>
+        <v>93417</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         <v>136591339</v>
       </c>
       <c r="B56" t="n">
-        <v>93415</v>
+        <v>93417</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7171,7 +7171,7 @@
         <v>136591297</v>
       </c>
       <c r="B59" t="n">
-        <v>93055</v>
+        <v>93057</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7283,7 +7283,7 @@
         <v>136591303</v>
       </c>
       <c r="B60" t="n">
-        <v>93055</v>
+        <v>93057</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
         <v>136591307</v>
       </c>
       <c r="B61" t="n">
-        <v>93055</v>
+        <v>93057</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         <v>136585526</v>
       </c>
       <c r="B62" t="n">
-        <v>93437</v>
+        <v>93439</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7619,7 +7619,7 @@
         <v>136585493</v>
       </c>
       <c r="B63" t="n">
-        <v>78879</v>
+        <v>78883</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7731,7 +7731,7 @@
         <v>136585494</v>
       </c>
       <c r="B64" t="n">
-        <v>78879</v>
+        <v>78883</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7843,7 +7843,7 @@
         <v>136585520</v>
       </c>
       <c r="B65" t="n">
-        <v>78879</v>
+        <v>78883</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         <v>136591289</v>
       </c>
       <c r="B66" t="n">
-        <v>78879</v>
+        <v>78883</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8067,7 +8067,7 @@
         <v>136591292</v>
       </c>
       <c r="B67" t="n">
-        <v>78879</v>
+        <v>78883</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8179,7 +8179,7 @@
         <v>136591299</v>
       </c>
       <c r="B68" t="n">
-        <v>78879</v>
+        <v>78883</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8291,7 +8291,7 @@
         <v>136591305</v>
       </c>
       <c r="B69" t="n">
-        <v>78879</v>
+        <v>78883</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8403,7 +8403,7 @@
         <v>136591308</v>
       </c>
       <c r="B70" t="n">
-        <v>78879</v>
+        <v>78883</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8515,7 +8515,7 @@
         <v>136591312</v>
       </c>
       <c r="B71" t="n">
-        <v>78879</v>
+        <v>78883</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8627,7 +8627,7 @@
         <v>136591318</v>
       </c>
       <c r="B72" t="n">
-        <v>78879</v>
+        <v>78883</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8739,7 +8739,7 @@
         <v>136591322</v>
       </c>
       <c r="B73" t="n">
-        <v>78879</v>
+        <v>78883</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         <v>136591325</v>
       </c>
       <c r="B74" t="n">
-        <v>78879</v>
+        <v>78883</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8963,7 +8963,7 @@
         <v>136591332</v>
       </c>
       <c r="B75" t="n">
-        <v>78879</v>
+        <v>78883</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9075,7 +9075,7 @@
         <v>136591337</v>
       </c>
       <c r="B76" t="n">
-        <v>78879</v>
+        <v>78883</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9187,7 +9187,7 @@
         <v>136591342</v>
       </c>
       <c r="B77" t="n">
-        <v>78879</v>
+        <v>78883</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9299,7 +9299,7 @@
         <v>136591348</v>
       </c>
       <c r="B78" t="n">
-        <v>78879</v>
+        <v>78883</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9411,7 +9411,7 @@
         <v>136591352</v>
       </c>
       <c r="B79" t="n">
-        <v>78879</v>
+        <v>78883</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9745,7 +9745,7 @@
         <v>136585487</v>
       </c>
       <c r="B82" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9857,7 +9857,7 @@
         <v>136585524</v>
       </c>
       <c r="B83" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9970,7 +9970,7 @@
         <v>136591288</v>
       </c>
       <c r="B84" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10082,7 +10082,7 @@
         <v>136591300</v>
       </c>
       <c r="B85" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10194,7 +10194,7 @@
         <v>136585513</v>
       </c>
       <c r="B86" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10306,7 +10306,7 @@
         <v>136585515</v>
       </c>
       <c r="B87" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10341,7 +10341,7 @@
         <v>714526</v>
       </c>
       <c r="R87" t="n">
-        <v>7335206</v>
+        <v>7335207</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -10418,7 +10418,7 @@
         <v>136591344</v>
       </c>
       <c r="B88" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10994,7 +10994,7 @@
         <v>136585501</v>
       </c>
       <c r="B93" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11106,7 +11106,7 @@
         <v>136585512</v>
       </c>
       <c r="B94" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11218,7 +11218,7 @@
         <v>136585523</v>
       </c>
       <c r="B95" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11330,7 +11330,7 @@
         <v>136585529</v>
       </c>
       <c r="B96" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11442,7 +11442,7 @@
         <v>136585532</v>
       </c>
       <c r="B97" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11554,7 +11554,7 @@
         <v>136591287</v>
       </c>
       <c r="B98" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11666,7 +11666,7 @@
         <v>136591306</v>
       </c>
       <c r="B99" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11778,7 +11778,7 @@
         <v>136591311</v>
       </c>
       <c r="B100" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11890,7 +11890,7 @@
         <v>136591317</v>
       </c>
       <c r="B101" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12002,7 +12002,7 @@
         <v>136591324</v>
       </c>
       <c r="B102" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12114,7 +12114,7 @@
         <v>136591350</v>
       </c>
       <c r="B103" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12226,7 +12226,7 @@
         <v>136591353</v>
       </c>
       <c r="B104" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12338,7 +12338,7 @@
         <v>136591355</v>
       </c>
       <c r="B105" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         <v>136591301</v>
       </c>
       <c r="B107" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12784,7 +12784,7 @@
         <v>136591313</v>
       </c>
       <c r="B109" t="n">
-        <v>93442</v>
+        <v>93444</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12908,7 +12908,7 @@
         <v>136591334</v>
       </c>
       <c r="B110" t="n">
-        <v>93442</v>
+        <v>93444</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13029,7 +13029,7 @@
         <v>136857936</v>
       </c>
       <c r="B111" t="n">
-        <v>93442</v>
+        <v>93444</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13150,7 +13150,7 @@
         <v>136591294</v>
       </c>
       <c r="B112" t="n">
-        <v>79499</v>
+        <v>79503</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13262,7 +13262,7 @@
         <v>136591321</v>
       </c>
       <c r="B113" t="n">
-        <v>79499</v>
+        <v>79503</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
         <v>136591341</v>
       </c>
       <c r="B114" t="n">
-        <v>79499</v>
+        <v>79503</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>

--- a/artfynd/A 32992-2026 artfynd.xlsx
+++ b/artfynd/A 32992-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136585485</v>
       </c>
       <c r="B2" t="n">
-        <v>92361</v>
+        <v>92363</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136585503</v>
       </c>
       <c r="B3" t="n">
-        <v>92361</v>
+        <v>92363</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136585525</v>
       </c>
       <c r="B4" t="n">
-        <v>92361</v>
+        <v>92363</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136591351</v>
       </c>
       <c r="B5" t="n">
-        <v>92361</v>
+        <v>92363</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136585531</v>
       </c>
       <c r="B6" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136591319</v>
       </c>
       <c r="B7" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>136858049</v>
       </c>
       <c r="B8" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>136858050</v>
       </c>
       <c r="B9" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>136857943</v>
       </c>
       <c r="B10" t="n">
-        <v>89377</v>
+        <v>89379</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>136585507</v>
       </c>
       <c r="B11" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>136591291</v>
       </c>
       <c r="B12" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>136585492</v>
       </c>
       <c r="B13" t="n">
-        <v>91119</v>
+        <v>91121</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>136585497</v>
       </c>
       <c r="B14" t="n">
-        <v>91119</v>
+        <v>91121</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         <v>136585498</v>
       </c>
       <c r="B15" t="n">
-        <v>91119</v>
+        <v>91121</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>136585514</v>
       </c>
       <c r="B16" t="n">
-        <v>91119</v>
+        <v>91121</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>136585517</v>
       </c>
       <c r="B17" t="n">
-        <v>91119</v>
+        <v>91121</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>136585528</v>
       </c>
       <c r="B18" t="n">
-        <v>91119</v>
+        <v>91121</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         <v>136585530</v>
       </c>
       <c r="B19" t="n">
-        <v>91119</v>
+        <v>91121</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>136585533</v>
       </c>
       <c r="B20" t="n">
-        <v>91119</v>
+        <v>91121</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>136591293</v>
       </c>
       <c r="B21" t="n">
-        <v>91119</v>
+        <v>91121</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
         <v>136591296</v>
       </c>
       <c r="B22" t="n">
-        <v>91119</v>
+        <v>91121</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>136591302</v>
       </c>
       <c r="B23" t="n">
-        <v>91119</v>
+        <v>91121</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         <v>136591331</v>
       </c>
       <c r="B24" t="n">
-        <v>91119</v>
+        <v>91121</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>136591333</v>
       </c>
       <c r="B25" t="n">
-        <v>91119</v>
+        <v>91121</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         <v>136857931</v>
       </c>
       <c r="B26" t="n">
-        <v>91119</v>
+        <v>91121</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>136591298</v>
       </c>
       <c r="B27" t="n">
-        <v>93429</v>
+        <v>93431</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>136591346</v>
       </c>
       <c r="B28" t="n">
-        <v>93429</v>
+        <v>93431</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3770,7 +3770,7 @@
         <v>136585490</v>
       </c>
       <c r="B29" t="n">
-        <v>92168</v>
+        <v>92170</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>136585499</v>
       </c>
       <c r="B30" t="n">
-        <v>92168</v>
+        <v>92170</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
         <v>136585516</v>
       </c>
       <c r="B31" t="n">
-        <v>92168</v>
+        <v>92170</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         <v>136585521</v>
       </c>
       <c r="B32" t="n">
-        <v>92168</v>
+        <v>92170</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4219,7 +4219,7 @@
         <v>136591340</v>
       </c>
       <c r="B33" t="n">
-        <v>92168</v>
+        <v>92170</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         <v>136585500</v>
       </c>
       <c r="B34" t="n">
-        <v>92037</v>
+        <v>92039</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4443,7 +4443,7 @@
         <v>136585506</v>
       </c>
       <c r="B35" t="n">
-        <v>92037</v>
+        <v>92039</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4666,7 +4666,7 @@
         <v>136585488</v>
       </c>
       <c r="B37" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>136585491</v>
       </c>
       <c r="B38" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         <v>136585495</v>
       </c>
       <c r="B39" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5002,7 +5002,7 @@
         <v>136585509</v>
       </c>
       <c r="B40" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         <v>136585518</v>
       </c>
       <c r="B41" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
         <v>136585522</v>
       </c>
       <c r="B42" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         <v>136585527</v>
       </c>
       <c r="B43" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         <v>136591316</v>
       </c>
       <c r="B44" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5562,7 +5562,7 @@
         <v>136591335</v>
       </c>
       <c r="B45" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5674,7 +5674,7 @@
         <v>136591338</v>
       </c>
       <c r="B46" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
         <v>136591345</v>
       </c>
       <c r="B47" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5915,7 +5915,7 @@
         <v>136591354</v>
       </c>
       <c r="B48" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         <v>136858053</v>
       </c>
       <c r="B49" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
         <v>136858054</v>
       </c>
       <c r="B50" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6269,7 +6269,7 @@
         <v>136858055</v>
       </c>
       <c r="B51" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6501,7 +6501,7 @@
         <v>136585489</v>
       </c>
       <c r="B53" t="n">
-        <v>93417</v>
+        <v>93419</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6613,7 +6613,7 @@
         <v>136591295</v>
       </c>
       <c r="B54" t="n">
-        <v>93417</v>
+        <v>93419</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         <v>136591314</v>
       </c>
       <c r="B55" t="n">
-        <v>93417</v>
+        <v>93419</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         <v>136591339</v>
       </c>
       <c r="B56" t="n">
-        <v>93417</v>
+        <v>93419</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7171,7 +7171,7 @@
         <v>136591297</v>
       </c>
       <c r="B59" t="n">
-        <v>93057</v>
+        <v>93059</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7283,7 +7283,7 @@
         <v>136591303</v>
       </c>
       <c r="B60" t="n">
-        <v>93057</v>
+        <v>93059</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
         <v>136591307</v>
       </c>
       <c r="B61" t="n">
-        <v>93057</v>
+        <v>93059</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         <v>136585526</v>
       </c>
       <c r="B62" t="n">
-        <v>93439</v>
+        <v>93441</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7619,7 +7619,7 @@
         <v>136585493</v>
       </c>
       <c r="B63" t="n">
-        <v>78883</v>
+        <v>78885</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7731,7 +7731,7 @@
         <v>136585494</v>
       </c>
       <c r="B64" t="n">
-        <v>78883</v>
+        <v>78885</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7843,7 +7843,7 @@
         <v>136585520</v>
       </c>
       <c r="B65" t="n">
-        <v>78883</v>
+        <v>78885</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         <v>136591289</v>
       </c>
       <c r="B66" t="n">
-        <v>78883</v>
+        <v>78885</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8067,7 +8067,7 @@
         <v>136591292</v>
       </c>
       <c r="B67" t="n">
-        <v>78883</v>
+        <v>78885</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8179,7 +8179,7 @@
         <v>136591299</v>
       </c>
       <c r="B68" t="n">
-        <v>78883</v>
+        <v>78885</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8291,7 +8291,7 @@
         <v>136591305</v>
       </c>
       <c r="B69" t="n">
-        <v>78883</v>
+        <v>78885</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8403,7 +8403,7 @@
         <v>136591308</v>
       </c>
       <c r="B70" t="n">
-        <v>78883</v>
+        <v>78885</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8515,7 +8515,7 @@
         <v>136591312</v>
       </c>
       <c r="B71" t="n">
-        <v>78883</v>
+        <v>78885</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8627,7 +8627,7 @@
         <v>136591318</v>
       </c>
       <c r="B72" t="n">
-        <v>78883</v>
+        <v>78885</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8739,7 +8739,7 @@
         <v>136591322</v>
       </c>
       <c r="B73" t="n">
-        <v>78883</v>
+        <v>78885</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         <v>136591325</v>
       </c>
       <c r="B74" t="n">
-        <v>78883</v>
+        <v>78885</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8963,7 +8963,7 @@
         <v>136591332</v>
       </c>
       <c r="B75" t="n">
-        <v>78883</v>
+        <v>78885</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9075,7 +9075,7 @@
         <v>136591337</v>
       </c>
       <c r="B76" t="n">
-        <v>78883</v>
+        <v>78885</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9187,7 +9187,7 @@
         <v>136591342</v>
       </c>
       <c r="B77" t="n">
-        <v>78883</v>
+        <v>78885</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9299,7 +9299,7 @@
         <v>136591348</v>
       </c>
       <c r="B78" t="n">
-        <v>78883</v>
+        <v>78885</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9411,7 +9411,7 @@
         <v>136591352</v>
       </c>
       <c r="B79" t="n">
-        <v>78883</v>
+        <v>78885</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9745,7 +9745,7 @@
         <v>136585487</v>
       </c>
       <c r="B82" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9857,7 +9857,7 @@
         <v>136585524</v>
       </c>
       <c r="B83" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9970,7 +9970,7 @@
         <v>136591288</v>
       </c>
       <c r="B84" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10082,7 +10082,7 @@
         <v>136591300</v>
       </c>
       <c r="B85" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10194,7 +10194,7 @@
         <v>136585513</v>
       </c>
       <c r="B86" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10306,7 +10306,7 @@
         <v>136585515</v>
       </c>
       <c r="B87" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10418,7 +10418,7 @@
         <v>136591344</v>
       </c>
       <c r="B88" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10530,7 +10530,7 @@
         <v>136591309</v>
       </c>
       <c r="B89" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10642,7 +10642,7 @@
         <v>136591323</v>
       </c>
       <c r="B90" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10994,7 +10994,7 @@
         <v>136585501</v>
       </c>
       <c r="B93" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11106,7 +11106,7 @@
         <v>136585512</v>
       </c>
       <c r="B94" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11218,7 +11218,7 @@
         <v>136585523</v>
       </c>
       <c r="B95" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11330,7 +11330,7 @@
         <v>136585529</v>
       </c>
       <c r="B96" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11442,7 +11442,7 @@
         <v>136585532</v>
       </c>
       <c r="B97" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11554,7 +11554,7 @@
         <v>136591287</v>
       </c>
       <c r="B98" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11666,7 +11666,7 @@
         <v>136591306</v>
       </c>
       <c r="B99" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11778,7 +11778,7 @@
         <v>136591311</v>
       </c>
       <c r="B100" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11890,7 +11890,7 @@
         <v>136591317</v>
       </c>
       <c r="B101" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12002,7 +12002,7 @@
         <v>136591324</v>
       </c>
       <c r="B102" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12114,7 +12114,7 @@
         <v>136591350</v>
       </c>
       <c r="B103" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12226,7 +12226,7 @@
         <v>136591353</v>
       </c>
       <c r="B104" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12338,7 +12338,7 @@
         <v>136591355</v>
       </c>
       <c r="B105" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         <v>136591301</v>
       </c>
       <c r="B107" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12784,7 +12784,7 @@
         <v>136591313</v>
       </c>
       <c r="B109" t="n">
-        <v>93444</v>
+        <v>93446</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12908,7 +12908,7 @@
         <v>136591334</v>
       </c>
       <c r="B110" t="n">
-        <v>93444</v>
+        <v>93446</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13029,7 +13029,7 @@
         <v>136857936</v>
       </c>
       <c r="B111" t="n">
-        <v>93444</v>
+        <v>93446</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13150,7 +13150,7 @@
         <v>136591294</v>
       </c>
       <c r="B112" t="n">
-        <v>79503</v>
+        <v>79505</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13262,7 +13262,7 @@
         <v>136591321</v>
       </c>
       <c r="B113" t="n">
-        <v>79503</v>
+        <v>79505</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
         <v>136591341</v>
       </c>
       <c r="B114" t="n">
-        <v>79503</v>
+        <v>79505</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>

--- a/artfynd/A 32992-2026 artfynd.xlsx
+++ b/artfynd/A 32992-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136585485</v>
       </c>
       <c r="B2" t="n">
-        <v>92363</v>
+        <v>92364</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136585503</v>
       </c>
       <c r="B3" t="n">
-        <v>92363</v>
+        <v>92364</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136585525</v>
       </c>
       <c r="B4" t="n">
-        <v>92363</v>
+        <v>92364</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136591351</v>
       </c>
       <c r="B5" t="n">
-        <v>92363</v>
+        <v>92364</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136585531</v>
       </c>
       <c r="B6" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136591319</v>
       </c>
       <c r="B7" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>136858049</v>
       </c>
       <c r="B8" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>136858050</v>
       </c>
       <c r="B9" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>136857943</v>
       </c>
       <c r="B10" t="n">
-        <v>89379</v>
+        <v>89380</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>136585507</v>
       </c>
       <c r="B11" t="n">
-        <v>92296</v>
+        <v>92297</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>136591291</v>
       </c>
       <c r="B12" t="n">
-        <v>92296</v>
+        <v>92297</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>136585492</v>
       </c>
       <c r="B13" t="n">
-        <v>91121</v>
+        <v>91122</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>136585497</v>
       </c>
       <c r="B14" t="n">
-        <v>91121</v>
+        <v>91122</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         <v>136585498</v>
       </c>
       <c r="B15" t="n">
-        <v>91121</v>
+        <v>91122</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>136585514</v>
       </c>
       <c r="B16" t="n">
-        <v>91121</v>
+        <v>91122</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>136585517</v>
       </c>
       <c r="B17" t="n">
-        <v>91121</v>
+        <v>91122</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>136585528</v>
       </c>
       <c r="B18" t="n">
-        <v>91121</v>
+        <v>91122</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         <v>136585530</v>
       </c>
       <c r="B19" t="n">
-        <v>91121</v>
+        <v>91122</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>136585533</v>
       </c>
       <c r="B20" t="n">
-        <v>91121</v>
+        <v>91122</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>136591293</v>
       </c>
       <c r="B21" t="n">
-        <v>91121</v>
+        <v>91122</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
         <v>136591296</v>
       </c>
       <c r="B22" t="n">
-        <v>91121</v>
+        <v>91122</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>136591302</v>
       </c>
       <c r="B23" t="n">
-        <v>91121</v>
+        <v>91122</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         <v>136591331</v>
       </c>
       <c r="B24" t="n">
-        <v>91121</v>
+        <v>91122</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>136591333</v>
       </c>
       <c r="B25" t="n">
-        <v>91121</v>
+        <v>91122</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         <v>136857931</v>
       </c>
       <c r="B26" t="n">
-        <v>91121</v>
+        <v>91122</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>136591298</v>
       </c>
       <c r="B27" t="n">
-        <v>93431</v>
+        <v>93432</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>136591346</v>
       </c>
       <c r="B28" t="n">
-        <v>93431</v>
+        <v>93432</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3770,7 +3770,7 @@
         <v>136585490</v>
       </c>
       <c r="B29" t="n">
-        <v>92170</v>
+        <v>92171</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>136585499</v>
       </c>
       <c r="B30" t="n">
-        <v>92170</v>
+        <v>92171</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
         <v>136585516</v>
       </c>
       <c r="B31" t="n">
-        <v>92170</v>
+        <v>92171</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         <v>136585521</v>
       </c>
       <c r="B32" t="n">
-        <v>92170</v>
+        <v>92171</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4219,7 +4219,7 @@
         <v>136591340</v>
       </c>
       <c r="B33" t="n">
-        <v>92170</v>
+        <v>92171</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         <v>136585500</v>
       </c>
       <c r="B34" t="n">
-        <v>92039</v>
+        <v>92040</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4443,7 +4443,7 @@
         <v>136585506</v>
       </c>
       <c r="B35" t="n">
-        <v>92039</v>
+        <v>92040</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4666,7 +4666,7 @@
         <v>136585488</v>
       </c>
       <c r="B37" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>136585491</v>
       </c>
       <c r="B38" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         <v>136585495</v>
       </c>
       <c r="B39" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5002,7 +5002,7 @@
         <v>136585509</v>
       </c>
       <c r="B40" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         <v>136585518</v>
       </c>
       <c r="B41" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
         <v>136585522</v>
       </c>
       <c r="B42" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         <v>136585527</v>
       </c>
       <c r="B43" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         <v>136591316</v>
       </c>
       <c r="B44" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5562,7 +5562,7 @@
         <v>136591335</v>
       </c>
       <c r="B45" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5674,7 +5674,7 @@
         <v>136591338</v>
       </c>
       <c r="B46" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
         <v>136591345</v>
       </c>
       <c r="B47" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5915,7 +5915,7 @@
         <v>136591354</v>
       </c>
       <c r="B48" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         <v>136858053</v>
       </c>
       <c r="B49" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
         <v>136858054</v>
       </c>
       <c r="B50" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6269,7 +6269,7 @@
         <v>136858055</v>
       </c>
       <c r="B51" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6501,7 +6501,7 @@
         <v>136585489</v>
       </c>
       <c r="B53" t="n">
-        <v>93419</v>
+        <v>93420</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6613,7 +6613,7 @@
         <v>136591295</v>
       </c>
       <c r="B54" t="n">
-        <v>93419</v>
+        <v>93420</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         <v>136591314</v>
       </c>
       <c r="B55" t="n">
-        <v>93419</v>
+        <v>93420</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         <v>136591339</v>
       </c>
       <c r="B56" t="n">
-        <v>93419</v>
+        <v>93420</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7171,7 +7171,7 @@
         <v>136591297</v>
       </c>
       <c r="B59" t="n">
-        <v>93059</v>
+        <v>93060</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7283,7 +7283,7 @@
         <v>136591303</v>
       </c>
       <c r="B60" t="n">
-        <v>93059</v>
+        <v>93060</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
         <v>136591307</v>
       </c>
       <c r="B61" t="n">
-        <v>93059</v>
+        <v>93060</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         <v>136585526</v>
       </c>
       <c r="B62" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7619,7 +7619,7 @@
         <v>136585493</v>
       </c>
       <c r="B63" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7731,7 +7731,7 @@
         <v>136585494</v>
       </c>
       <c r="B64" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7843,7 +7843,7 @@
         <v>136585520</v>
       </c>
       <c r="B65" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         <v>136591289</v>
       </c>
       <c r="B66" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8067,7 +8067,7 @@
         <v>136591292</v>
       </c>
       <c r="B67" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8179,7 +8179,7 @@
         <v>136591299</v>
       </c>
       <c r="B68" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8291,7 +8291,7 @@
         <v>136591305</v>
       </c>
       <c r="B69" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8403,7 +8403,7 @@
         <v>136591308</v>
       </c>
       <c r="B70" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8515,7 +8515,7 @@
         <v>136591312</v>
       </c>
       <c r="B71" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8627,7 +8627,7 @@
         <v>136591318</v>
       </c>
       <c r="B72" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8739,7 +8739,7 @@
         <v>136591322</v>
       </c>
       <c r="B73" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         <v>136591325</v>
       </c>
       <c r="B74" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8963,7 +8963,7 @@
         <v>136591332</v>
       </c>
       <c r="B75" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9075,7 +9075,7 @@
         <v>136591337</v>
       </c>
       <c r="B76" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9187,7 +9187,7 @@
         <v>136591342</v>
       </c>
       <c r="B77" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9299,7 +9299,7 @@
         <v>136591348</v>
       </c>
       <c r="B78" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9411,7 +9411,7 @@
         <v>136591352</v>
       </c>
       <c r="B79" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9745,7 +9745,7 @@
         <v>136585487</v>
       </c>
       <c r="B82" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9857,7 +9857,7 @@
         <v>136585524</v>
       </c>
       <c r="B83" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9970,7 +9970,7 @@
         <v>136591288</v>
       </c>
       <c r="B84" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10082,7 +10082,7 @@
         <v>136591300</v>
       </c>
       <c r="B85" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10194,7 +10194,7 @@
         <v>136585513</v>
       </c>
       <c r="B86" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10306,7 +10306,7 @@
         <v>136585515</v>
       </c>
       <c r="B87" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10418,7 +10418,7 @@
         <v>136591344</v>
       </c>
       <c r="B88" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10530,7 +10530,7 @@
         <v>136591309</v>
       </c>
       <c r="B89" t="n">
-        <v>78482</v>
+        <v>78483</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10642,7 +10642,7 @@
         <v>136591323</v>
       </c>
       <c r="B90" t="n">
-        <v>78482</v>
+        <v>78483</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10994,7 +10994,7 @@
         <v>136585501</v>
       </c>
       <c r="B93" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11106,7 +11106,7 @@
         <v>136585512</v>
       </c>
       <c r="B94" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11218,7 +11218,7 @@
         <v>136585523</v>
       </c>
       <c r="B95" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11330,7 +11330,7 @@
         <v>136585529</v>
       </c>
       <c r="B96" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11442,7 +11442,7 @@
         <v>136585532</v>
       </c>
       <c r="B97" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11554,7 +11554,7 @@
         <v>136591287</v>
       </c>
       <c r="B98" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11666,7 +11666,7 @@
         <v>136591306</v>
       </c>
       <c r="B99" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11778,7 +11778,7 @@
         <v>136591311</v>
       </c>
       <c r="B100" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11890,7 +11890,7 @@
         <v>136591317</v>
       </c>
       <c r="B101" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12002,7 +12002,7 @@
         <v>136591324</v>
       </c>
       <c r="B102" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12114,7 +12114,7 @@
         <v>136591350</v>
       </c>
       <c r="B103" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12226,7 +12226,7 @@
         <v>136591353</v>
       </c>
       <c r="B104" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12338,7 +12338,7 @@
         <v>136591355</v>
       </c>
       <c r="B105" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         <v>136591301</v>
       </c>
       <c r="B107" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12784,7 +12784,7 @@
         <v>136591313</v>
       </c>
       <c r="B109" t="n">
-        <v>93446</v>
+        <v>93447</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12908,7 +12908,7 @@
         <v>136591334</v>
       </c>
       <c r="B110" t="n">
-        <v>93446</v>
+        <v>93447</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13029,7 +13029,7 @@
         <v>136857936</v>
       </c>
       <c r="B111" t="n">
-        <v>93446</v>
+        <v>93447</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13150,7 +13150,7 @@
         <v>136591294</v>
       </c>
       <c r="B112" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13262,7 +13262,7 @@
         <v>136591321</v>
       </c>
       <c r="B113" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
         <v>136591341</v>
       </c>
       <c r="B114" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>

--- a/artfynd/A 32992-2026 artfynd.xlsx
+++ b/artfynd/A 32992-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136585485</v>
       </c>
       <c r="B2" t="n">
-        <v>92364</v>
+        <v>92370</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136585503</v>
       </c>
       <c r="B3" t="n">
-        <v>92364</v>
+        <v>92370</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136585525</v>
       </c>
       <c r="B4" t="n">
-        <v>92364</v>
+        <v>92370</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136591351</v>
       </c>
       <c r="B5" t="n">
-        <v>92364</v>
+        <v>92370</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>714526</v>
       </c>
       <c r="R7" t="n">
-        <v>7335207</v>
+        <v>7335206</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1602,7 +1602,7 @@
         <v>136857943</v>
       </c>
       <c r="B10" t="n">
-        <v>89380</v>
+        <v>89386</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>136585507</v>
       </c>
       <c r="B11" t="n">
-        <v>92297</v>
+        <v>92303</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>136591291</v>
       </c>
       <c r="B12" t="n">
-        <v>92297</v>
+        <v>92303</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>136585492</v>
       </c>
       <c r="B13" t="n">
-        <v>91122</v>
+        <v>91128</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>136585497</v>
       </c>
       <c r="B14" t="n">
-        <v>91122</v>
+        <v>91128</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         <v>136585498</v>
       </c>
       <c r="B15" t="n">
-        <v>91122</v>
+        <v>91128</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>136585514</v>
       </c>
       <c r="B16" t="n">
-        <v>91122</v>
+        <v>91128</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>136585517</v>
       </c>
       <c r="B17" t="n">
-        <v>91122</v>
+        <v>91128</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>136585528</v>
       </c>
       <c r="B18" t="n">
-        <v>91122</v>
+        <v>91128</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         <v>136585530</v>
       </c>
       <c r="B19" t="n">
-        <v>91122</v>
+        <v>91128</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>136585533</v>
       </c>
       <c r="B20" t="n">
-        <v>91122</v>
+        <v>91128</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>136591293</v>
       </c>
       <c r="B21" t="n">
-        <v>91122</v>
+        <v>91128</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
         <v>136591296</v>
       </c>
       <c r="B22" t="n">
-        <v>91122</v>
+        <v>91128</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>136591302</v>
       </c>
       <c r="B23" t="n">
-        <v>91122</v>
+        <v>91128</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         <v>136591331</v>
       </c>
       <c r="B24" t="n">
-        <v>91122</v>
+        <v>91128</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>136591333</v>
       </c>
       <c r="B25" t="n">
-        <v>91122</v>
+        <v>91128</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         <v>136857931</v>
       </c>
       <c r="B26" t="n">
-        <v>91122</v>
+        <v>91128</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>136591298</v>
       </c>
       <c r="B27" t="n">
-        <v>93432</v>
+        <v>93438</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>136591346</v>
       </c>
       <c r="B28" t="n">
-        <v>93432</v>
+        <v>93438</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3770,7 +3770,7 @@
         <v>136585490</v>
       </c>
       <c r="B29" t="n">
-        <v>92171</v>
+        <v>92177</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>136585499</v>
       </c>
       <c r="B30" t="n">
-        <v>92171</v>
+        <v>92177</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
         <v>136585516</v>
       </c>
       <c r="B31" t="n">
-        <v>92171</v>
+        <v>92177</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         <v>136585521</v>
       </c>
       <c r="B32" t="n">
-        <v>92171</v>
+        <v>92177</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4219,7 +4219,7 @@
         <v>136591340</v>
       </c>
       <c r="B33" t="n">
-        <v>92171</v>
+        <v>92177</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         <v>136585500</v>
       </c>
       <c r="B34" t="n">
-        <v>92040</v>
+        <v>92046</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4443,7 +4443,7 @@
         <v>136585506</v>
       </c>
       <c r="B35" t="n">
-        <v>92040</v>
+        <v>92046</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4666,7 +4666,7 @@
         <v>136585488</v>
       </c>
       <c r="B37" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>136585491</v>
       </c>
       <c r="B38" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         <v>136585495</v>
       </c>
       <c r="B39" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5002,7 +5002,7 @@
         <v>136585509</v>
       </c>
       <c r="B40" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         <v>136585518</v>
       </c>
       <c r="B41" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
         <v>136585522</v>
       </c>
       <c r="B42" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         <v>136585527</v>
       </c>
       <c r="B43" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         <v>136591316</v>
       </c>
       <c r="B44" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5562,7 +5562,7 @@
         <v>136591335</v>
       </c>
       <c r="B45" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5674,7 +5674,7 @@
         <v>136591338</v>
       </c>
       <c r="B46" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
         <v>136591345</v>
       </c>
       <c r="B47" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5915,7 +5915,7 @@
         <v>136591354</v>
       </c>
       <c r="B48" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         <v>136858053</v>
       </c>
       <c r="B49" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
         <v>136858054</v>
       </c>
       <c r="B50" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6269,7 +6269,7 @@
         <v>136858055</v>
       </c>
       <c r="B51" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6501,7 +6501,7 @@
         <v>136585489</v>
       </c>
       <c r="B53" t="n">
-        <v>93420</v>
+        <v>93426</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6613,7 +6613,7 @@
         <v>136591295</v>
       </c>
       <c r="B54" t="n">
-        <v>93420</v>
+        <v>93426</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         <v>136591314</v>
       </c>
       <c r="B55" t="n">
-        <v>93420</v>
+        <v>93426</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         <v>136591339</v>
       </c>
       <c r="B56" t="n">
-        <v>93420</v>
+        <v>93426</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7171,7 +7171,7 @@
         <v>136591297</v>
       </c>
       <c r="B59" t="n">
-        <v>93060</v>
+        <v>93066</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7283,7 +7283,7 @@
         <v>136591303</v>
       </c>
       <c r="B60" t="n">
-        <v>93060</v>
+        <v>93066</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
         <v>136591307</v>
       </c>
       <c r="B61" t="n">
-        <v>93060</v>
+        <v>93066</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         <v>136585526</v>
       </c>
       <c r="B62" t="n">
-        <v>93442</v>
+        <v>93448</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -10341,7 +10341,7 @@
         <v>714526</v>
       </c>
       <c r="R87" t="n">
-        <v>7335207</v>
+        <v>7335206</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -12784,7 +12784,7 @@
         <v>136591313</v>
       </c>
       <c r="B109" t="n">
-        <v>93447</v>
+        <v>93453</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12908,7 +12908,7 @@
         <v>136591334</v>
       </c>
       <c r="B110" t="n">
-        <v>93447</v>
+        <v>93453</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13029,7 +13029,7 @@
         <v>136857936</v>
       </c>
       <c r="B111" t="n">
-        <v>93447</v>
+        <v>93453</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>

--- a/artfynd/A 32992-2026 artfynd.xlsx
+++ b/artfynd/A 32992-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136585485</v>
       </c>
       <c r="B2" t="n">
-        <v>92370</v>
+        <v>92374</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136585503</v>
       </c>
       <c r="B3" t="n">
-        <v>92370</v>
+        <v>92374</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136585525</v>
       </c>
       <c r="B4" t="n">
-        <v>92370</v>
+        <v>92374</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136591351</v>
       </c>
       <c r="B5" t="n">
-        <v>92370</v>
+        <v>92374</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136585531</v>
       </c>
       <c r="B6" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136591319</v>
       </c>
       <c r="B7" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>136858049</v>
       </c>
       <c r="B8" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>136858050</v>
       </c>
       <c r="B9" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>136857943</v>
       </c>
       <c r="B10" t="n">
-        <v>89386</v>
+        <v>89390</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>136585507</v>
       </c>
       <c r="B11" t="n">
-        <v>92303</v>
+        <v>92307</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>136591291</v>
       </c>
       <c r="B12" t="n">
-        <v>92303</v>
+        <v>92307</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>136585492</v>
       </c>
       <c r="B13" t="n">
-        <v>91128</v>
+        <v>91132</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>136585497</v>
       </c>
       <c r="B14" t="n">
-        <v>91128</v>
+        <v>91132</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         <v>136585498</v>
       </c>
       <c r="B15" t="n">
-        <v>91128</v>
+        <v>91132</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>136585514</v>
       </c>
       <c r="B16" t="n">
-        <v>91128</v>
+        <v>91132</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>136585517</v>
       </c>
       <c r="B17" t="n">
-        <v>91128</v>
+        <v>91132</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>136585528</v>
       </c>
       <c r="B18" t="n">
-        <v>91128</v>
+        <v>91132</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         <v>136585530</v>
       </c>
       <c r="B19" t="n">
-        <v>91128</v>
+        <v>91132</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>136585533</v>
       </c>
       <c r="B20" t="n">
-        <v>91128</v>
+        <v>91132</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>136591293</v>
       </c>
       <c r="B21" t="n">
-        <v>91128</v>
+        <v>91132</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
         <v>136591296</v>
       </c>
       <c r="B22" t="n">
-        <v>91128</v>
+        <v>91132</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>136591302</v>
       </c>
       <c r="B23" t="n">
-        <v>91128</v>
+        <v>91132</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         <v>136591331</v>
       </c>
       <c r="B24" t="n">
-        <v>91128</v>
+        <v>91132</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>136591333</v>
       </c>
       <c r="B25" t="n">
-        <v>91128</v>
+        <v>91132</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         <v>136857931</v>
       </c>
       <c r="B26" t="n">
-        <v>91128</v>
+        <v>91132</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>136591298</v>
       </c>
       <c r="B27" t="n">
-        <v>93438</v>
+        <v>93442</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>136591346</v>
       </c>
       <c r="B28" t="n">
-        <v>93438</v>
+        <v>93442</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3770,7 +3770,7 @@
         <v>136585490</v>
       </c>
       <c r="B29" t="n">
-        <v>92177</v>
+        <v>92181</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>136585499</v>
       </c>
       <c r="B30" t="n">
-        <v>92177</v>
+        <v>92181</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
         <v>136585516</v>
       </c>
       <c r="B31" t="n">
-        <v>92177</v>
+        <v>92181</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         <v>136585521</v>
       </c>
       <c r="B32" t="n">
-        <v>92177</v>
+        <v>92181</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4219,7 +4219,7 @@
         <v>136591340</v>
       </c>
       <c r="B33" t="n">
-        <v>92177</v>
+        <v>92181</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         <v>136585500</v>
       </c>
       <c r="B34" t="n">
-        <v>92046</v>
+        <v>92050</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4443,7 +4443,7 @@
         <v>136585506</v>
       </c>
       <c r="B35" t="n">
-        <v>92046</v>
+        <v>92050</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4666,7 +4666,7 @@
         <v>136585488</v>
       </c>
       <c r="B37" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>136585491</v>
       </c>
       <c r="B38" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         <v>136585495</v>
       </c>
       <c r="B39" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5002,7 +5002,7 @@
         <v>136585509</v>
       </c>
       <c r="B40" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         <v>136585518</v>
       </c>
       <c r="B41" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
         <v>136585522</v>
       </c>
       <c r="B42" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         <v>136585527</v>
       </c>
       <c r="B43" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         <v>136591316</v>
       </c>
       <c r="B44" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5562,7 +5562,7 @@
         <v>136591335</v>
       </c>
       <c r="B45" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5674,7 +5674,7 @@
         <v>136591338</v>
       </c>
       <c r="B46" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
         <v>136591345</v>
       </c>
       <c r="B47" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5915,7 +5915,7 @@
         <v>136591354</v>
       </c>
       <c r="B48" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         <v>136858053</v>
       </c>
       <c r="B49" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
         <v>136858054</v>
       </c>
       <c r="B50" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6269,7 +6269,7 @@
         <v>136858055</v>
       </c>
       <c r="B51" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6501,7 +6501,7 @@
         <v>136585489</v>
       </c>
       <c r="B53" t="n">
-        <v>93426</v>
+        <v>93430</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6613,7 +6613,7 @@
         <v>136591295</v>
       </c>
       <c r="B54" t="n">
-        <v>93426</v>
+        <v>93430</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         <v>136591314</v>
       </c>
       <c r="B55" t="n">
-        <v>93426</v>
+        <v>93430</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         <v>136591339</v>
       </c>
       <c r="B56" t="n">
-        <v>93426</v>
+        <v>93430</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7171,7 +7171,7 @@
         <v>136591297</v>
       </c>
       <c r="B59" t="n">
-        <v>93066</v>
+        <v>93070</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7283,7 +7283,7 @@
         <v>136591303</v>
       </c>
       <c r="B60" t="n">
-        <v>93066</v>
+        <v>93070</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
         <v>136591307</v>
       </c>
       <c r="B61" t="n">
-        <v>93066</v>
+        <v>93070</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         <v>136585526</v>
       </c>
       <c r="B62" t="n">
-        <v>93448</v>
+        <v>93452</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7619,7 +7619,7 @@
         <v>136585493</v>
       </c>
       <c r="B63" t="n">
-        <v>78886</v>
+        <v>78888</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7731,7 +7731,7 @@
         <v>136585494</v>
       </c>
       <c r="B64" t="n">
-        <v>78886</v>
+        <v>78888</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7843,7 +7843,7 @@
         <v>136585520</v>
       </c>
       <c r="B65" t="n">
-        <v>78886</v>
+        <v>78888</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         <v>136591289</v>
       </c>
       <c r="B66" t="n">
-        <v>78886</v>
+        <v>78888</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8067,7 +8067,7 @@
         <v>136591292</v>
       </c>
       <c r="B67" t="n">
-        <v>78886</v>
+        <v>78888</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8179,7 +8179,7 @@
         <v>136591299</v>
       </c>
       <c r="B68" t="n">
-        <v>78886</v>
+        <v>78888</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8291,7 +8291,7 @@
         <v>136591305</v>
       </c>
       <c r="B69" t="n">
-        <v>78886</v>
+        <v>78888</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8403,7 +8403,7 @@
         <v>136591308</v>
       </c>
       <c r="B70" t="n">
-        <v>78886</v>
+        <v>78888</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8515,7 +8515,7 @@
         <v>136591312</v>
       </c>
       <c r="B71" t="n">
-        <v>78886</v>
+        <v>78888</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8627,7 +8627,7 @@
         <v>136591318</v>
       </c>
       <c r="B72" t="n">
-        <v>78886</v>
+        <v>78888</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8739,7 +8739,7 @@
         <v>136591322</v>
       </c>
       <c r="B73" t="n">
-        <v>78886</v>
+        <v>78888</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         <v>136591325</v>
       </c>
       <c r="B74" t="n">
-        <v>78886</v>
+        <v>78888</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8963,7 +8963,7 @@
         <v>136591332</v>
       </c>
       <c r="B75" t="n">
-        <v>78886</v>
+        <v>78888</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9075,7 +9075,7 @@
         <v>136591337</v>
       </c>
       <c r="B76" t="n">
-        <v>78886</v>
+        <v>78888</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9187,7 +9187,7 @@
         <v>136591342</v>
       </c>
       <c r="B77" t="n">
-        <v>78886</v>
+        <v>78888</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9299,7 +9299,7 @@
         <v>136591348</v>
       </c>
       <c r="B78" t="n">
-        <v>78886</v>
+        <v>78888</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9411,7 +9411,7 @@
         <v>136591352</v>
       </c>
       <c r="B79" t="n">
-        <v>78886</v>
+        <v>78888</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9745,7 +9745,7 @@
         <v>136585487</v>
       </c>
       <c r="B82" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9857,7 +9857,7 @@
         <v>136585524</v>
       </c>
       <c r="B83" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9970,7 +9970,7 @@
         <v>136591288</v>
       </c>
       <c r="B84" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10082,7 +10082,7 @@
         <v>136591300</v>
       </c>
       <c r="B85" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10194,7 +10194,7 @@
         <v>136585513</v>
       </c>
       <c r="B86" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10306,7 +10306,7 @@
         <v>136585515</v>
       </c>
       <c r="B87" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10418,7 +10418,7 @@
         <v>136591344</v>
       </c>
       <c r="B88" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10530,7 +10530,7 @@
         <v>136591309</v>
       </c>
       <c r="B89" t="n">
-        <v>78483</v>
+        <v>78485</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10642,7 +10642,7 @@
         <v>136591323</v>
       </c>
       <c r="B90" t="n">
-        <v>78483</v>
+        <v>78485</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10994,7 +10994,7 @@
         <v>136585501</v>
       </c>
       <c r="B93" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11106,7 +11106,7 @@
         <v>136585512</v>
       </c>
       <c r="B94" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11218,7 +11218,7 @@
         <v>136585523</v>
       </c>
       <c r="B95" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11330,7 +11330,7 @@
         <v>136585529</v>
       </c>
       <c r="B96" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11442,7 +11442,7 @@
         <v>136585532</v>
       </c>
       <c r="B97" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11554,7 +11554,7 @@
         <v>136591287</v>
       </c>
       <c r="B98" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11666,7 +11666,7 @@
         <v>136591306</v>
       </c>
       <c r="B99" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11778,7 +11778,7 @@
         <v>136591311</v>
       </c>
       <c r="B100" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11890,7 +11890,7 @@
         <v>136591317</v>
       </c>
       <c r="B101" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12002,7 +12002,7 @@
         <v>136591324</v>
       </c>
       <c r="B102" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12114,7 +12114,7 @@
         <v>136591350</v>
       </c>
       <c r="B103" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12226,7 +12226,7 @@
         <v>136591353</v>
       </c>
       <c r="B104" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12338,7 +12338,7 @@
         <v>136591355</v>
       </c>
       <c r="B105" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         <v>136591301</v>
       </c>
       <c r="B107" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12784,7 +12784,7 @@
         <v>136591313</v>
       </c>
       <c r="B109" t="n">
-        <v>93453</v>
+        <v>93457</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12908,7 +12908,7 @@
         <v>136591334</v>
       </c>
       <c r="B110" t="n">
-        <v>93453</v>
+        <v>93457</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13029,7 +13029,7 @@
         <v>136857936</v>
       </c>
       <c r="B111" t="n">
-        <v>93453</v>
+        <v>93457</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13150,7 +13150,7 @@
         <v>136591294</v>
       </c>
       <c r="B112" t="n">
-        <v>79506</v>
+        <v>79508</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13262,7 +13262,7 @@
         <v>136591321</v>
       </c>
       <c r="B113" t="n">
-        <v>79506</v>
+        <v>79508</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
         <v>136591341</v>
       </c>
       <c r="B114" t="n">
-        <v>79506</v>
+        <v>79508</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>

--- a/artfynd/A 32992-2026 artfynd.xlsx
+++ b/artfynd/A 32992-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136585485</v>
       </c>
       <c r="B2" t="n">
-        <v>92374</v>
+        <v>92376</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136585503</v>
       </c>
       <c r="B3" t="n">
-        <v>92374</v>
+        <v>92376</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136585525</v>
       </c>
       <c r="B4" t="n">
-        <v>92374</v>
+        <v>92376</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136591351</v>
       </c>
       <c r="B5" t="n">
-        <v>92374</v>
+        <v>92376</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136585531</v>
       </c>
       <c r="B6" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136591319</v>
       </c>
       <c r="B7" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>136858049</v>
       </c>
       <c r="B8" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>136858050</v>
       </c>
       <c r="B9" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>136857943</v>
       </c>
       <c r="B10" t="n">
-        <v>89390</v>
+        <v>89392</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>136585507</v>
       </c>
       <c r="B11" t="n">
-        <v>92307</v>
+        <v>92309</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>136591291</v>
       </c>
       <c r="B12" t="n">
-        <v>92307</v>
+        <v>92309</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>136585492</v>
       </c>
       <c r="B13" t="n">
-        <v>91132</v>
+        <v>91134</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>136585497</v>
       </c>
       <c r="B14" t="n">
-        <v>91132</v>
+        <v>91134</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         <v>136585498</v>
       </c>
       <c r="B15" t="n">
-        <v>91132</v>
+        <v>91134</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>136585514</v>
       </c>
       <c r="B16" t="n">
-        <v>91132</v>
+        <v>91134</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>136585517</v>
       </c>
       <c r="B17" t="n">
-        <v>91132</v>
+        <v>91134</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>136585528</v>
       </c>
       <c r="B18" t="n">
-        <v>91132</v>
+        <v>91134</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         <v>136585530</v>
       </c>
       <c r="B19" t="n">
-        <v>91132</v>
+        <v>91134</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>136585533</v>
       </c>
       <c r="B20" t="n">
-        <v>91132</v>
+        <v>91134</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>136591293</v>
       </c>
       <c r="B21" t="n">
-        <v>91132</v>
+        <v>91134</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
         <v>136591296</v>
       </c>
       <c r="B22" t="n">
-        <v>91132</v>
+        <v>91134</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>136591302</v>
       </c>
       <c r="B23" t="n">
-        <v>91132</v>
+        <v>91134</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         <v>136591331</v>
       </c>
       <c r="B24" t="n">
-        <v>91132</v>
+        <v>91134</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>136591333</v>
       </c>
       <c r="B25" t="n">
-        <v>91132</v>
+        <v>91134</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         <v>136857931</v>
       </c>
       <c r="B26" t="n">
-        <v>91132</v>
+        <v>91134</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>136591298</v>
       </c>
       <c r="B27" t="n">
-        <v>93442</v>
+        <v>93444</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>136591346</v>
       </c>
       <c r="B28" t="n">
-        <v>93442</v>
+        <v>93444</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3770,7 +3770,7 @@
         <v>136585490</v>
       </c>
       <c r="B29" t="n">
-        <v>92181</v>
+        <v>92183</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>136585499</v>
       </c>
       <c r="B30" t="n">
-        <v>92181</v>
+        <v>92183</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
         <v>136585516</v>
       </c>
       <c r="B31" t="n">
-        <v>92181</v>
+        <v>92183</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         <v>136585521</v>
       </c>
       <c r="B32" t="n">
-        <v>92181</v>
+        <v>92183</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4219,7 +4219,7 @@
         <v>136591340</v>
       </c>
       <c r="B33" t="n">
-        <v>92181</v>
+        <v>92183</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         <v>136585500</v>
       </c>
       <c r="B34" t="n">
-        <v>92050</v>
+        <v>92052</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4443,7 +4443,7 @@
         <v>136585506</v>
       </c>
       <c r="B35" t="n">
-        <v>92050</v>
+        <v>92052</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4666,7 +4666,7 @@
         <v>136585488</v>
       </c>
       <c r="B37" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>136585491</v>
       </c>
       <c r="B38" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         <v>136585495</v>
       </c>
       <c r="B39" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5002,7 +5002,7 @@
         <v>136585509</v>
       </c>
       <c r="B40" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         <v>136585518</v>
       </c>
       <c r="B41" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
         <v>136585522</v>
       </c>
       <c r="B42" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         <v>136585527</v>
       </c>
       <c r="B43" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         <v>136591316</v>
       </c>
       <c r="B44" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5562,7 +5562,7 @@
         <v>136591335</v>
       </c>
       <c r="B45" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5674,7 +5674,7 @@
         <v>136591338</v>
       </c>
       <c r="B46" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
         <v>136591345</v>
       </c>
       <c r="B47" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5915,7 +5915,7 @@
         <v>136591354</v>
       </c>
       <c r="B48" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         <v>136858053</v>
       </c>
       <c r="B49" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
         <v>136858054</v>
       </c>
       <c r="B50" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6269,7 +6269,7 @@
         <v>136858055</v>
       </c>
       <c r="B51" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6501,7 +6501,7 @@
         <v>136585489</v>
       </c>
       <c r="B53" t="n">
-        <v>93430</v>
+        <v>93432</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6613,7 +6613,7 @@
         <v>136591295</v>
       </c>
       <c r="B54" t="n">
-        <v>93430</v>
+        <v>93432</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         <v>136591314</v>
       </c>
       <c r="B55" t="n">
-        <v>93430</v>
+        <v>93432</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         <v>136591339</v>
       </c>
       <c r="B56" t="n">
-        <v>93430</v>
+        <v>93432</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7171,7 +7171,7 @@
         <v>136591297</v>
       </c>
       <c r="B59" t="n">
-        <v>93070</v>
+        <v>93072</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7283,7 +7283,7 @@
         <v>136591303</v>
       </c>
       <c r="B60" t="n">
-        <v>93070</v>
+        <v>93072</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
         <v>136591307</v>
       </c>
       <c r="B61" t="n">
-        <v>93070</v>
+        <v>93072</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         <v>136585526</v>
       </c>
       <c r="B62" t="n">
-        <v>93452</v>
+        <v>93454</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7619,7 +7619,7 @@
         <v>136585493</v>
       </c>
       <c r="B63" t="n">
-        <v>78888</v>
+        <v>78891</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7731,7 +7731,7 @@
         <v>136585494</v>
       </c>
       <c r="B64" t="n">
-        <v>78888</v>
+        <v>78891</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7843,7 +7843,7 @@
         <v>136585520</v>
       </c>
       <c r="B65" t="n">
-        <v>78888</v>
+        <v>78891</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         <v>136591289</v>
       </c>
       <c r="B66" t="n">
-        <v>78888</v>
+        <v>78891</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8067,7 +8067,7 @@
         <v>136591292</v>
       </c>
       <c r="B67" t="n">
-        <v>78888</v>
+        <v>78891</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8179,7 +8179,7 @@
         <v>136591299</v>
       </c>
       <c r="B68" t="n">
-        <v>78888</v>
+        <v>78891</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8291,7 +8291,7 @@
         <v>136591305</v>
       </c>
       <c r="B69" t="n">
-        <v>78888</v>
+        <v>78891</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8403,7 +8403,7 @@
         <v>136591308</v>
       </c>
       <c r="B70" t="n">
-        <v>78888</v>
+        <v>78891</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8515,7 +8515,7 @@
         <v>136591312</v>
       </c>
       <c r="B71" t="n">
-        <v>78888</v>
+        <v>78891</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8627,7 +8627,7 @@
         <v>136591318</v>
       </c>
       <c r="B72" t="n">
-        <v>78888</v>
+        <v>78891</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8739,7 +8739,7 @@
         <v>136591322</v>
       </c>
       <c r="B73" t="n">
-        <v>78888</v>
+        <v>78891</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         <v>136591325</v>
       </c>
       <c r="B74" t="n">
-        <v>78888</v>
+        <v>78891</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8963,7 +8963,7 @@
         <v>136591332</v>
       </c>
       <c r="B75" t="n">
-        <v>78888</v>
+        <v>78891</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9075,7 +9075,7 @@
         <v>136591337</v>
       </c>
       <c r="B76" t="n">
-        <v>78888</v>
+        <v>78891</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9187,7 +9187,7 @@
         <v>136591342</v>
       </c>
       <c r="B77" t="n">
-        <v>78888</v>
+        <v>78891</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9299,7 +9299,7 @@
         <v>136591348</v>
       </c>
       <c r="B78" t="n">
-        <v>78888</v>
+        <v>78891</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9411,7 +9411,7 @@
         <v>136591352</v>
       </c>
       <c r="B79" t="n">
-        <v>78888</v>
+        <v>78891</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9745,7 +9745,7 @@
         <v>136585487</v>
       </c>
       <c r="B82" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9857,7 +9857,7 @@
         <v>136585524</v>
       </c>
       <c r="B83" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9970,7 +9970,7 @@
         <v>136591288</v>
       </c>
       <c r="B84" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10082,7 +10082,7 @@
         <v>136591300</v>
       </c>
       <c r="B85" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10194,7 +10194,7 @@
         <v>136585513</v>
       </c>
       <c r="B86" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10306,7 +10306,7 @@
         <v>136585515</v>
       </c>
       <c r="B87" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10418,7 +10418,7 @@
         <v>136591344</v>
       </c>
       <c r="B88" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10530,7 +10530,7 @@
         <v>136591309</v>
       </c>
       <c r="B89" t="n">
-        <v>78485</v>
+        <v>78488</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10642,7 +10642,7 @@
         <v>136591323</v>
       </c>
       <c r="B90" t="n">
-        <v>78485</v>
+        <v>78488</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10994,7 +10994,7 @@
         <v>136585501</v>
       </c>
       <c r="B93" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11106,7 +11106,7 @@
         <v>136585512</v>
       </c>
       <c r="B94" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11218,7 +11218,7 @@
         <v>136585523</v>
       </c>
       <c r="B95" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11330,7 +11330,7 @@
         <v>136585529</v>
       </c>
       <c r="B96" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11442,7 +11442,7 @@
         <v>136585532</v>
       </c>
       <c r="B97" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11554,7 +11554,7 @@
         <v>136591287</v>
       </c>
       <c r="B98" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11666,7 +11666,7 @@
         <v>136591306</v>
       </c>
       <c r="B99" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11778,7 +11778,7 @@
         <v>136591311</v>
       </c>
       <c r="B100" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11890,7 +11890,7 @@
         <v>136591317</v>
       </c>
       <c r="B101" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12002,7 +12002,7 @@
         <v>136591324</v>
       </c>
       <c r="B102" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12114,7 +12114,7 @@
         <v>136591350</v>
       </c>
       <c r="B103" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12226,7 +12226,7 @@
         <v>136591353</v>
       </c>
       <c r="B104" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12338,7 +12338,7 @@
         <v>136591355</v>
       </c>
       <c r="B105" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         <v>136591301</v>
       </c>
       <c r="B107" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12784,7 +12784,7 @@
         <v>136591313</v>
       </c>
       <c r="B109" t="n">
-        <v>93457</v>
+        <v>93459</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12908,7 +12908,7 @@
         <v>136591334</v>
       </c>
       <c r="B110" t="n">
-        <v>93457</v>
+        <v>93459</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13029,7 +13029,7 @@
         <v>136857936</v>
       </c>
       <c r="B111" t="n">
-        <v>93457</v>
+        <v>93459</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13150,7 +13150,7 @@
         <v>136591294</v>
       </c>
       <c r="B112" t="n">
-        <v>79508</v>
+        <v>79511</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13262,7 +13262,7 @@
         <v>136591321</v>
       </c>
       <c r="B113" t="n">
-        <v>79508</v>
+        <v>79511</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
         <v>136591341</v>
       </c>
       <c r="B114" t="n">
-        <v>79508</v>
+        <v>79511</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>

--- a/artfynd/A 32992-2026 artfynd.xlsx
+++ b/artfynd/A 32992-2026 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>136591351</v>
       </c>
       <c r="B5" t="n">
-        <v>92376</v>
+        <v>92389</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136591319</v>
       </c>
       <c r="B7" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>136858049</v>
       </c>
       <c r="B8" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>136858050</v>
       </c>
       <c r="B9" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>136857943</v>
       </c>
       <c r="B10" t="n">
-        <v>89392</v>
+        <v>89405</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>136591291</v>
       </c>
       <c r="B12" t="n">
-        <v>92309</v>
+        <v>92322</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>136591293</v>
       </c>
       <c r="B21" t="n">
-        <v>91134</v>
+        <v>91147</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
         <v>136591296</v>
       </c>
       <c r="B22" t="n">
-        <v>91134</v>
+        <v>91147</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>136591302</v>
       </c>
       <c r="B23" t="n">
-        <v>91134</v>
+        <v>91147</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         <v>136591331</v>
       </c>
       <c r="B24" t="n">
-        <v>91134</v>
+        <v>91147</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>136591333</v>
       </c>
       <c r="B25" t="n">
-        <v>91134</v>
+        <v>91147</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         <v>136857931</v>
       </c>
       <c r="B26" t="n">
-        <v>91134</v>
+        <v>91147</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>136591298</v>
       </c>
       <c r="B27" t="n">
-        <v>93444</v>
+        <v>93457</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>136591346</v>
       </c>
       <c r="B28" t="n">
-        <v>93444</v>
+        <v>93457</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4219,7 +4219,7 @@
         <v>136591340</v>
       </c>
       <c r="B33" t="n">
-        <v>92183</v>
+        <v>92196</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         <v>136591316</v>
       </c>
       <c r="B44" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5562,7 +5562,7 @@
         <v>136591335</v>
       </c>
       <c r="B45" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5674,7 +5674,7 @@
         <v>136591338</v>
       </c>
       <c r="B46" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
         <v>136591345</v>
       </c>
       <c r="B47" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5915,7 +5915,7 @@
         <v>136591354</v>
       </c>
       <c r="B48" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         <v>136858053</v>
       </c>
       <c r="B49" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
         <v>136858054</v>
       </c>
       <c r="B50" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6269,7 +6269,7 @@
         <v>136858055</v>
       </c>
       <c r="B51" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6613,7 +6613,7 @@
         <v>136591295</v>
       </c>
       <c r="B54" t="n">
-        <v>93432</v>
+        <v>93445</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         <v>136591314</v>
       </c>
       <c r="B55" t="n">
-        <v>93432</v>
+        <v>93445</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         <v>136591339</v>
       </c>
       <c r="B56" t="n">
-        <v>93432</v>
+        <v>93445</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7171,7 +7171,7 @@
         <v>136591297</v>
       </c>
       <c r="B59" t="n">
-        <v>93072</v>
+        <v>93085</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7283,7 +7283,7 @@
         <v>136591303</v>
       </c>
       <c r="B60" t="n">
-        <v>93072</v>
+        <v>93085</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
         <v>136591307</v>
       </c>
       <c r="B61" t="n">
-        <v>93072</v>
+        <v>93085</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         <v>136591289</v>
       </c>
       <c r="B66" t="n">
-        <v>78891</v>
+        <v>78904</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8067,7 +8067,7 @@
         <v>136591292</v>
       </c>
       <c r="B67" t="n">
-        <v>78891</v>
+        <v>78904</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8179,7 +8179,7 @@
         <v>136591299</v>
       </c>
       <c r="B68" t="n">
-        <v>78891</v>
+        <v>78904</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8291,7 +8291,7 @@
         <v>136591305</v>
       </c>
       <c r="B69" t="n">
-        <v>78891</v>
+        <v>78904</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8403,7 +8403,7 @@
         <v>136591308</v>
       </c>
       <c r="B70" t="n">
-        <v>78891</v>
+        <v>78904</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8515,7 +8515,7 @@
         <v>136591312</v>
       </c>
       <c r="B71" t="n">
-        <v>78891</v>
+        <v>78904</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8627,7 +8627,7 @@
         <v>136591318</v>
       </c>
       <c r="B72" t="n">
-        <v>78891</v>
+        <v>78904</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8739,7 +8739,7 @@
         <v>136591322</v>
       </c>
       <c r="B73" t="n">
-        <v>78891</v>
+        <v>78904</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         <v>136591325</v>
       </c>
       <c r="B74" t="n">
-        <v>78891</v>
+        <v>78904</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8963,7 +8963,7 @@
         <v>136591332</v>
       </c>
       <c r="B75" t="n">
-        <v>78891</v>
+        <v>78904</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9075,7 +9075,7 @@
         <v>136591337</v>
       </c>
       <c r="B76" t="n">
-        <v>78891</v>
+        <v>78904</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9187,7 +9187,7 @@
         <v>136591342</v>
       </c>
       <c r="B77" t="n">
-        <v>78891</v>
+        <v>78904</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9299,7 +9299,7 @@
         <v>136591348</v>
       </c>
       <c r="B78" t="n">
-        <v>78891</v>
+        <v>78904</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9411,7 +9411,7 @@
         <v>136591352</v>
       </c>
       <c r="B79" t="n">
-        <v>78891</v>
+        <v>78904</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9970,7 +9970,7 @@
         <v>136591288</v>
       </c>
       <c r="B84" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10082,7 +10082,7 @@
         <v>136591300</v>
       </c>
       <c r="B85" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10418,7 +10418,7 @@
         <v>136591344</v>
       </c>
       <c r="B88" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10530,7 +10530,7 @@
         <v>136591309</v>
       </c>
       <c r="B89" t="n">
-        <v>78488</v>
+        <v>78501</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10642,7 +10642,7 @@
         <v>136591323</v>
       </c>
       <c r="B90" t="n">
-        <v>78488</v>
+        <v>78501</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10754,7 +10754,7 @@
         <v>136591343</v>
       </c>
       <c r="B91" t="n">
-        <v>57195</v>
+        <v>57208</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10874,7 +10874,7 @@
         <v>136591304</v>
       </c>
       <c r="B92" t="n">
-        <v>58112</v>
+        <v>58125</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11554,7 +11554,7 @@
         <v>136591287</v>
       </c>
       <c r="B98" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11666,7 +11666,7 @@
         <v>136591306</v>
       </c>
       <c r="B99" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11778,7 +11778,7 @@
         <v>136591311</v>
       </c>
       <c r="B100" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11890,7 +11890,7 @@
         <v>136591317</v>
       </c>
       <c r="B101" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12002,7 +12002,7 @@
         <v>136591324</v>
       </c>
       <c r="B102" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12114,7 +12114,7 @@
         <v>136591350</v>
       </c>
       <c r="B103" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12226,7 +12226,7 @@
         <v>136591353</v>
       </c>
       <c r="B104" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12338,7 +12338,7 @@
         <v>136591355</v>
       </c>
       <c r="B105" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         <v>136591301</v>
       </c>
       <c r="B107" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12784,7 +12784,7 @@
         <v>136591313</v>
       </c>
       <c r="B109" t="n">
-        <v>93459</v>
+        <v>93472</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12908,7 +12908,7 @@
         <v>136591334</v>
       </c>
       <c r="B110" t="n">
-        <v>93459</v>
+        <v>93472</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13029,7 +13029,7 @@
         <v>136857936</v>
       </c>
       <c r="B111" t="n">
-        <v>93459</v>
+        <v>93472</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13150,7 +13150,7 @@
         <v>136591294</v>
       </c>
       <c r="B112" t="n">
-        <v>79511</v>
+        <v>79524</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13262,7 +13262,7 @@
         <v>136591321</v>
       </c>
       <c r="B113" t="n">
-        <v>79511</v>
+        <v>79524</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
         <v>136591341</v>
       </c>
       <c r="B114" t="n">
-        <v>79511</v>
+        <v>79524</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>

--- a/artfynd/A 32992-2026 artfynd.xlsx
+++ b/artfynd/A 32992-2026 artfynd.xlsx
@@ -1360,7 +1360,7 @@
         <v>136858049</v>
       </c>
       <c r="B8" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>136858050</v>
       </c>
       <c r="B9" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>136857943</v>
       </c>
       <c r="B10" t="n">
-        <v>89405</v>
+        <v>89407</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
         <v>136591296</v>
       </c>
       <c r="B22" t="n">
-        <v>91147</v>
+        <v>91149</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         <v>136857931</v>
       </c>
       <c r="B26" t="n">
-        <v>91147</v>
+        <v>91149</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         <v>136858053</v>
       </c>
       <c r="B49" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
         <v>136858054</v>
       </c>
       <c r="B50" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6269,7 +6269,7 @@
         <v>136858055</v>
       </c>
       <c r="B51" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -13029,7 +13029,7 @@
         <v>136857936</v>
       </c>
       <c r="B111" t="n">
-        <v>93472</v>
+        <v>93473</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>

--- a/artfynd/A 32992-2026 artfynd.xlsx
+++ b/artfynd/A 32992-2026 artfynd.xlsx
@@ -1602,7 +1602,7 @@
         <v>136857943</v>
       </c>
       <c r="B10" t="n">
-        <v>89407</v>
+        <v>89410</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
         <v>136591296</v>
       </c>
       <c r="B22" t="n">
-        <v>91149</v>
+        <v>91152</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         <v>136857931</v>
       </c>
       <c r="B26" t="n">
-        <v>91149</v>
+        <v>91152</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         <v>136858053</v>
       </c>
       <c r="B49" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
         <v>136858054</v>
       </c>
       <c r="B50" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6269,7 +6269,7 @@
         <v>136858055</v>
       </c>
       <c r="B51" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -13029,7 +13029,7 @@
         <v>136857936</v>
       </c>
       <c r="B111" t="n">
-        <v>93473</v>
+        <v>93476</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>

--- a/artfynd/A 32992-2026 artfynd.xlsx
+++ b/artfynd/A 32992-2026 artfynd.xlsx
@@ -1360,7 +1360,7 @@
         <v>136858049</v>
       </c>
       <c r="B8" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>136858050</v>
       </c>
       <c r="B9" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>136857943</v>
       </c>
       <c r="B10" t="n">
-        <v>89410</v>
+        <v>89420</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         <v>136857931</v>
       </c>
       <c r="B26" t="n">
-        <v>91152</v>
+        <v>91162</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         <v>136858053</v>
       </c>
       <c r="B49" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
         <v>136858054</v>
       </c>
       <c r="B50" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6269,7 +6269,7 @@
         <v>136858055</v>
       </c>
       <c r="B51" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -13029,7 +13029,7 @@
         <v>136857936</v>
       </c>
       <c r="B111" t="n">
-        <v>93476</v>
+        <v>93486</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>

--- a/artfynd/A 32992-2026 artfynd.xlsx
+++ b/artfynd/A 32992-2026 artfynd.xlsx
@@ -1602,7 +1602,7 @@
         <v>136857943</v>
       </c>
       <c r="B10" t="n">
-        <v>89420</v>
+        <v>89421</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         <v>136857931</v>
       </c>
       <c r="B26" t="n">
-        <v>91162</v>
+        <v>91163</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         <v>136858053</v>
       </c>
       <c r="B49" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
         <v>136858054</v>
       </c>
       <c r="B50" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6269,7 +6269,7 @@
         <v>136858055</v>
       </c>
       <c r="B51" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -13029,7 +13029,7 @@
         <v>136857936</v>
       </c>
       <c r="B111" t="n">
-        <v>93486</v>
+        <v>93487</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>

--- a/artfynd/A 32992-2026 artfynd.xlsx
+++ b/artfynd/A 32992-2026 artfynd.xlsx
@@ -1360,7 +1360,7 @@
         <v>136858049</v>
       </c>
       <c r="B8" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>136858050</v>
       </c>
       <c r="B9" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>136857943</v>
       </c>
       <c r="B10" t="n">
-        <v>89421</v>
+        <v>89424</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         <v>136857931</v>
       </c>
       <c r="B26" t="n">
-        <v>91163</v>
+        <v>91166</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         <v>136858053</v>
       </c>
       <c r="B49" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
         <v>136858054</v>
       </c>
       <c r="B50" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6269,7 +6269,7 @@
         <v>136858055</v>
       </c>
       <c r="B51" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -13029,7 +13029,7 @@
         <v>136857936</v>
       </c>
       <c r="B111" t="n">
-        <v>93487</v>
+        <v>93492</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>

--- a/artfynd/A 32992-2026 artfynd.xlsx
+++ b/artfynd/A 32992-2026 artfynd.xlsx
@@ -3408,7 +3408,7 @@
         <v>136857931</v>
       </c>
       <c r="B26" t="n">
-        <v>91166</v>
+        <v>91168</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         <v>136858053</v>
       </c>
       <c r="B49" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
         <v>136858054</v>
       </c>
       <c r="B50" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6269,7 +6269,7 @@
         <v>136858055</v>
       </c>
       <c r="B51" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -13029,7 +13029,7 @@
         <v>136857936</v>
       </c>
       <c r="B111" t="n">
-        <v>93492</v>
+        <v>93494</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>

--- a/artfynd/A 32992-2026 artfynd.xlsx
+++ b/artfynd/A 32992-2026 artfynd.xlsx
@@ -1360,7 +1360,7 @@
         <v>136858049</v>
       </c>
       <c r="B8" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>136858050</v>
       </c>
       <c r="B9" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>136857943</v>
       </c>
       <c r="B10" t="n">
-        <v>89424</v>
+        <v>89429</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         <v>136857931</v>
       </c>
       <c r="B26" t="n">
-        <v>91168</v>
+        <v>91173</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         <v>136858053</v>
       </c>
       <c r="B49" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
         <v>136858054</v>
       </c>
       <c r="B50" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6269,7 +6269,7 @@
         <v>136858055</v>
       </c>
       <c r="B51" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -13029,7 +13029,7 @@
         <v>136857936</v>
       </c>
       <c r="B111" t="n">
-        <v>93494</v>
+        <v>93500</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
